--- a/data/synthetic/qa/audit_sample/rater_a_sheet.xlsx
+++ b/data/synthetic/qa/audit_sample/rater_a_sheet.xlsx
@@ -1,39 +1,73 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\MoodNote\MoodNote-AI\data\synthetic\qa\audit_sample\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B0005F-81FB-46E3-92F5-90A41FD63FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11F960F-CED8-42F5-9252-68544B62A0D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Rater1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="370">
   <si>
     <t>sample_id</t>
   </si>
   <si>
+    <t>Enjoyment</t>
+  </si>
+  <si>
     <t>text</t>
   </si>
   <si>
+    <t>Sadness</t>
+  </si>
+  <si>
     <t>label</t>
   </si>
   <si>
+    <t>Anger</t>
+  </si>
+  <si>
+    <t>Fear</t>
+  </si>
+  <si>
+    <t>Disgust</t>
+  </si>
+  <si>
+    <t>Surprise</t>
+  </si>
+  <si>
     <t>llama-3-8b-instruct-0-8c7bc26209</t>
   </si>
   <si>
+    <t>Other</t>
+  </si>
+  <si>
     <t>Hôm nay tôi đã có một ngày đầy ắp niềm vui. Tôi đi với những người bạn thân và chúng tôi có một bữa ăn tối tuyệt vời. Chúng tôi trò chuyện, cười và có một giờ phút thật vui vẻ. Tôi cảm thấy nhẹ hơn, như thể những phiền hức của mình đã được giải quyết. Tuy nhiên, điều kỳ diệu nhất là tôi cảm thấy mình đã trưởng thành hơn một chút, như thể tôi đã học được một bài học mới. Maybe it's because I've been taking care of myself lately, or maybe it's because I've been surrounding myself with good people, but whatever the reason, I'm grateful for this sense of growth and accomplishment.</t>
   </si>
   <si>
@@ -70,120 +104,120 @@
     <t>llama-3-8b-instruct-1-d0615fff7c</t>
   </si>
   <si>
+    <t>qwen3-8b-2-d7298d6873</t>
+  </si>
+  <si>
+    <t>Buổi sáng nay tôi phải ngồi vào bàn làm việc với một tâm trạng như đang mang trong người một quả bom. Nguyên nhân là vì mình đã giải thích rõ ràng, tỉ mỉ về cái lỗi trong file dữ liệu, nhưng không ai thèm nghe, cứ như thể mình đang nói chuyện với một bức tường vậy. Tôi chả biết nữa, có lẽ vì mình nói chuyện quá nhiều, nên cả phòng toàn lắc đầu như kiểu đang xem một bộ phim hài. Sáng nay tôi chỉ muốn ngồi im một mình, ăn từng miếng bánh mì kẹp thịt, và tự nhủ rằng mình sẽ không bao giờ nói chuyện nhiều như vậy nữa — cho dù trong công việc thì có phải cũng không.</t>
+  </si>
+  <si>
+    <t>qwen3-8b-5-065f6f4c35</t>
+  </si>
+  <si>
+    <t>Khi vừa mới mở cửa ra, tôi thấy anh ấy đứng đó, tay nắm chặt cửa như đợi lâu rồi. Cái cảm giác đó, như một cái kết thúc chưa kịp nói ra, khiến tim mình đập thình thịch mà không hiểu vì sao.</t>
+  </si>
+  <si>
+    <t>qwen3-8b-3-0a27f108a6</t>
+  </si>
+  <si>
+    <t>Tối qua, tôi thức đến gần sáng vì lo lắng về buổi thuyết trình ngày mai, sợ mình sẽ nói sai điều gì đó, sợ sự cố ngoài ý muốn xảy ra, khiến mọi thứ trở nên tồi tệ hơn mong đợi.</t>
+  </si>
+  <si>
+    <t>qwen3-8b-5-481db69245</t>
+  </si>
+  <si>
+    <t>Buổi sáng hôm nay trời mưa tầm tã, cứ như ai đó đang đổ nước lên đầu mình vậy, lạnh lùng và không chút cảm thông. Tôi đang bận rộn chuẩn bị cho ngày học, thì đột nhiên có một tin nhắn đến, khiến tôi ngay lập tức giật mình – không phải vì tin nhắn, mà vì người gửi. Một người quen từ năm xưa, giờ đã lâu không liên lạc, đột ngột xuất hiện trong tin nhắn với nội dung khiến tôi không thể tin vào mắt mình. Cái cảm giác như đang mơ, mà lại không phải là giấc mơ. Tôi lẩm cẩm trong đầu, vừa cười vừa khóc, vì sao lại đến lúc này, cái thời điểm tôi đang cố gắng tập trung để không trễ giờ học. Chắc là trời cũng muốn trêu tôi, khiến tôi phải cười, rồi lại thở dài, vì sự bất ngờ này thật sự là một cú sốc thật sự.</t>
+  </si>
+  <si>
+    <t>llama-3-8b-instruct-0-871c9fb3ab</t>
+  </si>
+  <si>
+    <t>Tạt về nhà với túi xách gần đầy. Hôm nay chúng tôi và đám bạn thân đi ăn, bỏ ra một chút tiền, nhưng quả thực giá trị. Tựa như không có tiền đâu, chúng tôi còn hơn thế. Nhiều chuyện có thể nói, nhiều cười có thể có. Tự nhiên thấy nhẹ, không còn lo lắng về tiền nữa.</t>
+  </si>
+  <si>
+    <t>qwen3-8b-3-4b1f0db064</t>
+  </si>
+  <si>
+    <t>Sáng nay đi chợ với mẹ, tôi cố gắng không cười khi bà mua cả thảy 5 kg hành tây, 3 kg cà chua và 2 kg dưa chuột — tất cả đều như thể chúng là một phần của chương trình "Mua nhiều để giảm giá". Tôi không biết mình đang đi mua đồ hay tham gia một cuộc thi "Ai mua nhiều nhất" cho gia đình.</t>
+  </si>
+  <si>
+    <t>qwen3-8b-1-4ff526d7e6</t>
+  </si>
+  <si>
+    <t>Mình mua cái áo đó hôm qua mà hôm nay mới thấy mình không cần, tiền cũng đã ra hết rồi, buồn luôn.</t>
+  </si>
+  <si>
+    <t>qwen3-8b-4-32f6b55fc3</t>
+  </si>
+  <si>
+    <t>Sáng nay trong lúc thực tập, mình bắt gặp một đồng nghiệp vừa ném một mẩu giấy bẩn ra sàn hành lang, không hề để ý đến sự phản cảm của hành vi đó. Cảm giác thật khó chịu, như thể cái sự vô tâm ấy đang chọc vào từng khớp xương trong lòng mình.</t>
+  </si>
+  <si>
+    <t>qwen3-8b-0-3af11d0241</t>
+  </si>
+  <si>
+    <t>Hôm nay mình có một khoảnh khắc thật sự đáng nhớ, dù có vẻ như là một sự cố ngoài ý muốn. Khi đang lướt mạng xã hội, mình vô tình lướt đến một nhóm bạn cũ, đột nhiên nhớ ra mình từng có một mối quan hệ kỳ cục với họ. Bỗng chốc, mình bị cuốn vào một cơn hoang tưởng, tưởng mình đang trở lại thời điểm ấy, cười đùa với họ như cũ. Cảm giác như mình đã được 'trở lại' một ngày nào đó, dù thực ra đó chỉ là một giấc mộng ngắn ngủi. Thật ra, mình cũng không hiểu vì sao lại thấy vui đến thế, có lẽ vì mình đã quá mệt mỏi với những thứ khác, nên khoảnh khắc ấy, dù là ảo, cũng khiến mình thấy nhẹ nhõm, như được giải phóng khỏi cái vỏ cứng nhắc của ngày.</t>
+  </si>
+  <si>
+    <t>qwen3-8b-5-46f11ef65b</t>
+  </si>
+  <si>
+    <t>Sáng nay đang ngồi làm bài trong công ty thì đột ngột bị trưởng phòng gọi đến văn phòng. Mình tưởng là có lỗi gì, nhưng không ngờ lại được thông báo mình đã được nhận vào làm thực tập chính thức. Đầu tiên là shock, tưởng mình nghe nhầm, phải kiểm tra lại email và tin nhắn vài lần. Cảm giác như mơ, nhưng khi thấy cái lịch làm việc và giấy nhận việc thì mình biết là thật. Nhìn đồng nghiệp thì ai nấy đều vui vẻ, có người còn chúc mừng. Mình chỉ biết cười, không hiểu sao lại cảm thấy hạnh phúc đến vậy.</t>
+  </si>
+  <si>
+    <t>qwen3-8b-4-f8239ffe21</t>
+  </si>
+  <si>
+    <t>Sáng nay, mình đã hoàn thành được một dự án nhỏ mà mình đã lăn lụy suốt tuần qua. Khi nhìn lại những gì mình đã làm, cảm giác buồn bã và ghê tởm bỗng trào lên. Thành công thật sự có thể đến, nhưng đôi khi mình thấy mình như đang gặm một thứ gì đó dở tệ, không có gì vui vẻ.</t>
+  </si>
+  <si>
+    <t>qwen3-8b-1-7027b5bd87</t>
+  </si>
+  <si>
+    <t>Hôm nay mình dậy muộn, đầu óc nặng như chèo nước, chân tay tê liệt như vừa qua trận. Không biết vì sao, chỉ là cảm giác mệt mỏi kéo dài, không muốn mở mắt, không muốn ăn uống. Mình tự hỏi liệu có phải vì mệt hay vì lòng mình đang trống rỗng, không còn cảm thấy gì cả.</t>
+  </si>
+  <si>
+    <t>qwen3-8b-1-73caca1a26</t>
+  </si>
+  <si>
+    <t>Tối nay mình không ngủ được, cứ nghĩ lại chuyện ấy, lòng như vỡ ra, buồn quá không biết làm sao. Mình không hiểu vì sao mình lại yếu đuối thế, nhưng có lẽ vì tình yêu ấy đã thật sự không còn, mà mình lại không dám đối mặt với sự thật.</t>
+  </si>
+  <si>
+    <t>llama-3-8b-instruct-3-23f89580c0</t>
+  </si>
+  <si>
+    <t>Tôi không bao giờ tin rằng ngày mai sẽ đến, nhưng lại lo lắng đến tận cỡ. Mẹ lại nói với tôi rằng cuộc sống là một chuỗi những quyết định, nhưng tôi lại không biết đâu là quyết định của mình. Giờ, tôi đang lo lắng đến việc đi học, đến việc chọn trường, đến việc chọn con đường học tập... Tất tần tật đều bị kiểm soát bởi quyết định của mình. Có khi nào tôi cảm thấy mình bị nhấn chìm trong những lo lắng đó. ðŸ¤¸</t>
+  </si>
+  <si>
+    <t>llama-3-8b-instruct-1-75d172aee4</t>
+  </si>
+  <si>
+    <t>Mẹ gọi tên tôi vào tối hôm qua, nhưng tôi không đáp. Cậu dâu họ đang ở lại nhà, và họ lại nói nhau. Tôi không hiểu sao, nhưng cảm giác trong lòng lại trào lên. Tôi không muốn nghe nữa, không muốn thấy họ nữa. Mẹ hỏi tôi tại sao tôi không đáp, tôi không biết trả lời. Cảm giác buồn lại đè lên, và tôi cứ ngồi đó, không dậy.
+ Tôi không hiểu tại sao họ lại nói nhau thế. Tôi không hiểu tại sao họ lại phải nói nhau. Tôi không hiểu tại sao họ lại không lại để tôi yên. Tôi cảm thấy buồn, mệt, và choáng. Tôi không muốn nghe nữa, tôi không muốn nói nữa. Cảm giác trong lòng cứ trào lên, và tôi cứ khóc.</t>
+  </si>
+  <si>
+    <t>llama-3-8b-instruct-2-3d973e7d9d</t>
+  </si>
+  <si>
+    <t>Tôi vừa đi khám bệnh và lại bị người khác giải thích sai. Càng tức hơn, chỉ muốn nói thẳng với họ nhưng không dám. Cảm giác như có lửa đốt trong người, khó để kiểm soát.</t>
+  </si>
+  <si>
+    <t>llama-3-8b-instruct-2-5498923bb4</t>
+  </si>
+  <si>
+    <t>Tôi cảm thấy giận tởm sau một cuộc họp khó khăn với một số công sự. Đến nay, tôi vẫn chưa thể hiểu lý do họ không chịu lắng nghe mình giải thích, dù tôi đã nói rất rõ ràng và cụ thể. Khi nghĩ về vấn đề này, tôi càng tức giận hơn. Tôi chỉ muốn đóng cửa lại và ngồi im một lúc để hạ hỏa. Nhưng sau cùng, tôi biết điều này không phải là giải pháp. Tôi phải tiếp tục làm việc và tìm cách vượt qua khó khăn này.</t>
+  </si>
+  <si>
+    <t>qwen3-8b-0-479bdd00f0</t>
+  </si>
+  <si>
+    <t>Hôm nay đi làm về thấy buồn quá, không biết vì sao. Dù đã cố gắng quên đi chuyện cũ nhưng cứ nghĩ đến anh ấy là tim như bị ai đó bóp nhẹ, hụt hana. Mình không hiểu vì sao lại để mình đau như thế, có lẽ vì anh ấy quá tốt, quá dịu dàng, khiến mình không thể gạt ra khỏi tâm trí. Buổi tối thì mình cố gắng cười, cố gắng làm như không sao, nhưng trong lòng thì đau thấu. Có những ngày mình muốn khóc, muốn chạy trốn, nhưng rồi lại cười, rồi lại cố gắng sống tiếp. Có lẽ mình cần phải học cách buông bỏ, nhưng sao lại khó thế nhỉ?</t>
+  </si>
+  <si>
+    <t>llama-3-8b-instruct-3-b634c1de53</t>
+  </si>
+  <si>
     <t>Mình ngồi ở cạnh cửa sổ, ngắm nhìn chiều tối. Cảm giác chán nản, không muốn làm gì. nghĩ lại chuyện lúc sáng, thấy những câu chuyện của mình với anh, những giấc mơ, những niềm tin. Đang tưởng anh sẽ quay lại, sẽ nói với mình, sẽ chia sẻ những điều đó. Nhưng giờ anh không còn là ai, và mình lại phải tiếp tục sống trong những giấc mơ, trong những nấc vọng.
-Mình không biết vì sao mình lại buồn thế, vì sao mình lại nhớ anh đến như thế. Dường như mình không thể quên được anh, không thể quên được những giấc mơ của mình với anh. Mình đã nghĩ rằng anh sẽ quay lại, nhưng giờ mình lại phải chấp nhận rằng anh đã đi, và mình không thể làm gì để thay đổi điều đó. Mình chỉ có thể nhớ anh, và sống trong những giấc mơ của mình với anh.</t>
-  </si>
-  <si>
-    <t>qwen3-8b-2-d7298d6873</t>
-  </si>
-  <si>
-    <t>Buổi sáng nay tôi phải ngồi vào bàn làm việc với một tâm trạng như đang mang trong người một quả bom. Nguyên nhân là vì mình đã giải thích rõ ràng, tỉ mỉ về cái lỗi trong file dữ liệu, nhưng không ai thèm nghe, cứ như thể mình đang nói chuyện với một bức tường vậy. Tôi chả biết nữa, có lẽ vì mình nói chuyện quá nhiều, nên cả phòng toàn lắc đầu như kiểu đang xem một bộ phim hài. Sáng nay tôi chỉ muốn ngồi im một mình, ăn từng miếng bánh mì kẹp thịt, và tự nhủ rằng mình sẽ không bao giờ nói chuyện nhiều như vậy nữa — cho dù trong công việc thì có phải cũng không.</t>
-  </si>
-  <si>
-    <t>qwen3-8b-5-065f6f4c35</t>
-  </si>
-  <si>
-    <t>Khi vừa mới mở cửa ra, tôi thấy anh ấy đứng đó, tay nắm chặt cửa như đợi lâu rồi. Cái cảm giác đó, như một cái kết thúc chưa kịp nói ra, khiến tim mình đập thình thịch mà không hiểu vì sao.</t>
-  </si>
-  <si>
-    <t>qwen3-8b-3-0a27f108a6</t>
-  </si>
-  <si>
-    <t>Tối qua, tôi thức đến gần sáng vì lo lắng về buổi thuyết trình ngày mai, sợ mình sẽ nói sai điều gì đó, sợ sự cố ngoài ý muốn xảy ra, khiến mọi thứ trở nên tồi tệ hơn mong đợi.</t>
-  </si>
-  <si>
-    <t>qwen3-8b-5-481db69245</t>
-  </si>
-  <si>
-    <t>Buổi sáng hôm nay trời mưa tầm tã, cứ như ai đó đang đổ nước lên đầu mình vậy, lạnh lùng và không chút cảm thông. Tôi đang bận rộn chuẩn bị cho ngày học, thì đột nhiên có một tin nhắn đến, khiến tôi ngay lập tức giật mình – không phải vì tin nhắn, mà vì người gửi. Một người quen từ năm xưa, giờ đã lâu không liên lạc, đột ngột xuất hiện trong tin nhắn với nội dung khiến tôi không thể tin vào mắt mình. Cái cảm giác như đang mơ, mà lại không phải là giấc mơ. Tôi lẩm cẩm trong đầu, vừa cười vừa khóc, vì sao lại đến lúc này, cái thời điểm tôi đang cố gắng tập trung để không trễ giờ học. Chắc là trời cũng muốn trêu tôi, khiến tôi phải cười, rồi lại thở dài, vì sự bất ngờ này thật sự là một cú sốc thật sự.</t>
-  </si>
-  <si>
-    <t>llama-3-8b-instruct-0-871c9fb3ab</t>
-  </si>
-  <si>
-    <t>Tạt về nhà với túi xách gần đầy. Hôm nay chúng tôi và đám bạn thân đi ăn, bỏ ra một chút tiền, nhưng quả thực giá trị. Tựa như không có tiền đâu, chúng tôi còn hơn thế. Nhiều chuyện có thể nói, nhiều cười có thể có. Tự nhiên thấy nhẹ, không còn lo lắng về tiền nữa.</t>
-  </si>
-  <si>
-    <t>qwen3-8b-3-4b1f0db064</t>
-  </si>
-  <si>
-    <t>Sáng nay đi chợ với mẹ, tôi cố gắng không cười khi bà mua cả thảy 5 kg hành tây, 3 kg cà chua và 2 kg dưa chuột — tất cả đều như thể chúng là một phần của chương trình "Mua nhiều để giảm giá". Tôi không biết mình đang đi mua đồ hay tham gia một cuộc thi "Ai mua nhiều nhất" cho gia đình.</t>
-  </si>
-  <si>
-    <t>qwen3-8b-1-4ff526d7e6</t>
-  </si>
-  <si>
-    <t>Mình mua cái áo đó hôm qua mà hôm nay mới thấy mình không cần, tiền cũng đã ra hết rồi, buồn luôn.</t>
-  </si>
-  <si>
-    <t>qwen3-8b-4-32f6b55fc3</t>
-  </si>
-  <si>
-    <t>Sáng nay trong lúc thực tập, mình bắt gặp một đồng nghiệp vừa ném một mẩu giấy bẩn ra sàn hành lang, không hề để ý đến sự phản cảm của hành vi đó. Cảm giác thật khó chịu, như thể cái sự vô tâm ấy đang chọc vào từng khớp xương trong lòng mình.</t>
-  </si>
-  <si>
-    <t>qwen3-8b-0-3af11d0241</t>
-  </si>
-  <si>
-    <t>Hôm nay mình có một khoảnh khắc thật sự đáng nhớ, dù có vẻ như là một sự cố ngoài ý muốn. Khi đang lướt mạng xã hội, mình vô tình lướt đến một nhóm bạn cũ, đột nhiên nhớ ra mình từng có một mối quan hệ kỳ cục với họ. Bỗng chốc, mình bị cuốn vào một cơn hoang tưởng, tưởng mình đang trở lại thời điểm ấy, cười đùa với họ như cũ. Cảm giác như mình đã được 'trở lại' một ngày nào đó, dù thực ra đó chỉ là một giấc mộng ngắn ngủi. Thật ra, mình cũng không hiểu vì sao lại thấy vui đến thế, có lẽ vì mình đã quá mệt mỏi với những thứ khác, nên khoảnh khắc ấy, dù là ảo, cũng khiến mình thấy nhẹ nhõm, như được giải phóng khỏi cái vỏ cứng nhắc của ngày.</t>
-  </si>
-  <si>
-    <t>qwen3-8b-5-46f11ef65b</t>
-  </si>
-  <si>
-    <t>Sáng nay đang ngồi làm bài trong công ty thì đột ngột bị trưởng phòng gọi đến văn phòng. Mình tưởng là có lỗi gì, nhưng không ngờ lại được thông báo mình đã được nhận vào làm thực tập chính thức. Đầu tiên là shock, tưởng mình nghe nhầm, phải kiểm tra lại email và tin nhắn vài lần. Cảm giác như mơ, nhưng khi thấy cái lịch làm việc và giấy nhận việc thì mình biết là thật. Nhìn đồng nghiệp thì ai nấy đều vui vẻ, có người còn chúc mừng. Mình chỉ biết cười, không hiểu sao lại cảm thấy hạnh phúc đến vậy.</t>
-  </si>
-  <si>
-    <t>qwen3-8b-4-f8239ffe21</t>
-  </si>
-  <si>
-    <t>Sáng nay, mình đã hoàn thành được một dự án nhỏ mà mình đã lăn lụy suốt tuần qua. Khi nhìn lại những gì mình đã làm, cảm giác buồn bã và ghê tởm bỗng trào lên. Thành công thật sự có thể đến, nhưng đôi khi mình thấy mình như đang gặm một thứ gì đó dở tệ, không có gì vui vẻ.</t>
-  </si>
-  <si>
-    <t>qwen3-8b-1-7027b5bd87</t>
-  </si>
-  <si>
-    <t>Hôm nay mình dậy muộn, đầu óc nặng như chèo nước, chân tay tê liệt như vừa qua trận. Không biết vì sao, chỉ là cảm giác mệt mỏi kéo dài, không muốn mở mắt, không muốn ăn uống. Mình tự hỏi liệu có phải vì mệt hay vì lòng mình đang trống rỗng, không còn cảm thấy gì cả.</t>
-  </si>
-  <si>
-    <t>qwen3-8b-1-73caca1a26</t>
-  </si>
-  <si>
-    <t>Tối nay mình không ngủ được, cứ nghĩ lại chuyện ấy, lòng như vỡ ra, buồn quá không biết làm sao. Mình không hiểu vì sao mình lại yếu đuối thế, nhưng có lẽ vì tình yêu ấy đã thật sự không còn, mà mình lại không dám đối mặt với sự thật.</t>
-  </si>
-  <si>
-    <t>llama-3-8b-instruct-3-23f89580c0</t>
-  </si>
-  <si>
-    <t>Tôi không bao giờ tin rằng ngày mai sẽ đến, nhưng lại lo lắng đến tận cỡ. Mẹ lại nói với tôi rằng cuộc sống là một chuỗi những quyết định, nhưng tôi lại không biết đâu là quyết định của mình. Giờ, tôi đang lo lắng đến việc đi học, đến việc chọn trường, đến việc chọn con đường học tập... Tất tần tật đều bị kiểm soát bởi quyết định của mình. Có khi nào tôi cảm thấy mình bị nhấn chìm trong những lo lắng đó. ðŸ¤¸</t>
-  </si>
-  <si>
-    <t>llama-3-8b-instruct-1-75d172aee4</t>
-  </si>
-  <si>
-    <t>Mẹ gọi tên tôi vào tối hôm qua, nhưng tôi không đáp. Cậu dâu họ đang ở lại nhà, và họ lại nói nhau. Tôi không hiểu sao, nhưng cảm giác trong lòng lại trào lên. Tôi không muốn nghe nữa, không muốn thấy họ nữa. Mẹ hỏi tôi tại sao tôi không đáp, tôi không biết trả lời. Cảm giác buồn lại đè lên, và tôi cứ ngồi đó, không dậy.
-Tôi không hiểu tại sao họ lại nói nhau thế. Tôi không hiểu tại sao họ lại phải nói nhau. Tôi không hiểu tại sao họ lại không lại để tôi yên. Tôi cảm thấy buồn, mệt, và choáng. Tôi không muốn nghe nữa, tôi không muốn nói nữa. Cảm giác trong lòng cứ trào lên, và tôi cứ khóc.</t>
-  </si>
-  <si>
-    <t>llama-3-8b-instruct-2-3d973e7d9d</t>
-  </si>
-  <si>
-    <t>Tôi vừa đi khám bệnh và lại bị người khác giải thích sai. Càng tức hơn, chỉ muốn nói thẳng với họ nhưng không dám. Cảm giác như có lửa đốt trong người, khó để kiểm soát.</t>
-  </si>
-  <si>
-    <t>llama-3-8b-instruct-2-5498923bb4</t>
-  </si>
-  <si>
-    <t>Tôi cảm thấy giận tởm sau một cuộc họp khó khăn với một số công sự. Đến nay, tôi vẫn chưa thể hiểu lý do họ không chịu lắng nghe mình giải thích, dù tôi đã nói rất rõ ràng và cụ thể. Khi nghĩ về vấn đề này, tôi càng tức giận hơn. Tôi chỉ muốn đóng cửa lại và ngồi im một lúc để hạ hỏa. Nhưng sau cùng, tôi biết điều này không phải là giải pháp. Tôi phải tiếp tục làm việc và tìm cách vượt qua khó khăn này.</t>
-  </si>
-  <si>
-    <t>qwen3-8b-0-479bdd00f0</t>
-  </si>
-  <si>
-    <t>Hôm nay đi làm về thấy buồn quá, không biết vì sao. Dù đã cố gắng quên đi chuyện cũ nhưng cứ nghĩ đến anh ấy là tim như bị ai đó bóp nhẹ, hụt hana. Mình không hiểu vì sao lại để mình đau như thế, có lẽ vì anh ấy quá tốt, quá dịu dàng, khiến mình không thể gạt ra khỏi tâm trí. Buổi tối thì mình cố gắng cười, cố gắng làm như không sao, nhưng trong lòng thì đau thấu. Có những ngày mình muốn khóc, muốn chạy trốn, nhưng rồi lại cười, rồi lại cố gắng sống tiếp. Có lẽ mình cần phải học cách buông bỏ, nhưng sao lại khó thế nhỉ?</t>
-  </si>
-  <si>
-    <t>llama-3-8b-instruct-3-b634c1de53</t>
+ Mình không biết vì sao mình lại buồn thế, vì sao mình lại nhớ anh đến như thế. Dường như mình không thể quên được anh, không thể quên được những giấc mơ của mình với anh. Mình đã nghĩ rằng anh sẽ quay lại, nhưng giờ mình lại phải chấp nhận rằng anh đã đi, và mình không thể làm gì để thay đổi điều đó. Mình chỉ có thể nhớ anh, và sống trong những giấc mơ của mình với anh.</t>
   </si>
   <si>
     <t>Tôi lại lo lắng không yên như thường. Đùa với chuyện tương lai, xem xem mình sẽ làm gì sau này. Mẹo của mình không chuẩn bị kịp, sợ mọi thứ vượt ngoài tầm kiểm soát. Nhiệm vụ dự thi của trường chỉ còn vài tuần, và mình lại chưa có kế hoạch cụ thể. Tim mình đập nhanh, thần giã, lo lắng bận tâm. Càng nghĩ về tương lai, càng lo lắng hơn. Mình cần tìm cách tập trung, cần tìm cách giải quyết vấn đề. Mình cần tìm ra con đường cụ thể để hướng tới tương lai.</t>
@@ -217,7 +251,7 @@
   </si>
   <si>
     <t>Mẹ gọi điện nói mẹ ơi, mẹ lại dối với con. Cứ nói con có thể hiểu, nhưng thực ra mẹ lại không tin con. Con đã giải thích nhiều lần, nhưng mẹ lại không lắng nghe. Con thậm chí đã ngắt điện, nhưng mẹ lại không để con yên. Con chán nản, không biết mẹ có phải là ai.
-Con nhớ ngày xưa, mẹ lại không tin con, con đã buồn lắm. Con cố gắng sống với hiện tại, nhưng con không thể quên. Con không thể quên lần mẹ lại dối với con. Con không thể quên mẹ lại không tin con. Con chán nản, con không biết mẹ có phải là ai. Con cảm thấy mình bị mẹ từ chối, con cảm thấy mình không được tin. Con cảm thấy mẹ lại không hiểu con. Con cảm thấy con không thể nào sống với mẹ.</t>
+ Con nhớ ngày xưa, mẹ lại không tin con, con đã buồn lắm. Con cố gắng sống với hiện tại, nhưng con không thể quên. Con không thể quên lần mẹ lại dối với con. Con không thể quên mẹ lại không tin con. Con chán nản, con không biết mẹ có phải là ai. Con cảm thấy mình bị mẹ từ chối, con cảm thấy mình không được tin. Con cảm thấy mẹ lại không hiểu con. Con cảm thấy con không thể nào sống với mẹ.</t>
   </si>
   <si>
     <t>qwen3-8b-0-df3eabd89b</t>
@@ -284,23 +318,23 @@
   </si>
   <si>
     <t>Tôi lại ngồi trong im lặng, không có chút hứng thú nào. Cảm giác buồn ngột ngạt và sâu sắc cứ tràn lên, như một tảng đá chìm vào trong tim. Tôi không hiểu tại sao tôi lại cảm thấy như vậy, như thể toàn bộ thế giới đã biến mất khỏi tầm tay.
-Nó có thể do những chuyện hồi tưởng vềesterday, những suy nghĩ và những cảm xúc sâu thẳm đã được đè ngã trong tôi. Tôi lại nhớ đến những lúc anh chị em tôi đã bỏ nhau, những lúc anh bỏ mẹ, những lúc mẹ lại đau ốm. Tất cả những thứ đã được lưu trữ trong tôi, và giờ nó đã trở thành một khối đá chìm trong tim tôi.
-Tôi không muốn nghĩ về những điều cũ, nhưng tôi lại không thể quên. Nó cứ lơ lững trong tôi, như một đám mây đen che khu vực, không cho tôi có chút niềm tin về tương lai. Tất cả những điều đã qua, những điều sẽ qua, và tôi lại trở thành người bỏ đói, không có bất kỳ điều gì để tin tưởng.</t>
+ Nó có thể do những chuyện hồi tưởng vềesterday, những suy nghĩ và những cảm xúc sâu thẳm đã được đè ngã trong tôi. Tôi lại nhớ đến những lúc anh chị em tôi đã bỏ nhau, những lúc anh bỏ mẹ, những lúc mẹ lại đau ốm. Tất cả những thứ đã được lưu trữ trong tôi, và giờ nó đã trở thành một khối đá chìm trong tim tôi.
+ Tôi không muốn nghĩ về những điều cũ, nhưng tôi lại không thể quên. Nó cứ lơ lững trong tôi, như một đám mây đen che khu vực, không cho tôi có chút niềm tin về tương lai. Tất cả những điều đã qua, những điều sẽ qua, và tôi lại trở thành người bỏ đói, không có bất kỳ điều gì để tin tưởng.</t>
   </si>
   <si>
     <t>llama-3-8b-instruct-3-4107c10927</t>
   </si>
   <si>
     <t>Tôi vừa qua một ngày học tập rất dài và đầy căng. Cảm giác lo lắng trong tôi đã trở nên rõ ràng hơn bao giờ hết. Dường như cứ mỗi phút, cứ mỗi giây, tôi đều bị quặc đi về tương lai. Ngày mai, tôi sẽ phải trải qua kì thi quan trọng, và nghĩ đến nó đã khiến tôi cảm thấy rất lo lắng.
-Tim tôi đập nhanh, khát khao để tìm ra một giải pháp để tự tin hơn. Nhưng những điều lo lắng cứ tiếp tục xâm nhập vào trí nhớ tôi, làm cho tôi trở nên phân tán và khó tập trung. Tôi cảm thấy mình không chuẩn bị kịp, và những điều lo lắng cứ tiếp tục tăng cao.
-Tôi hiểu rằng lo lắng là bình thường, nhưng cảm giác này đã trở nên quá mạnh mẽ trong tôi. Tôi cần tìm ra cách để vượt qua lo lắng và tìm lại sự tự tin. Sắp tới kì thi, tôi hy vọng có thể kiểm soát được cảm giác lo lắng và trở thành người tự tin hơn.</t>
+ Tim tôi đập nhanh, khát khao để tìm ra một giải pháp để tự tin hơn. Nhưng những điều lo lắng cứ tiếp tục xâm nhập vào trí nhớ tôi, làm cho tôi trở nên phân tán và khó tập trung. Tôi cảm thấy mình không chuẩn bị kịp, và những điều lo lắng cứ tiếp tục tăng cao.
+ Tôi hiểu rằng lo lắng là bình thường, nhưng cảm giác này đã trở nên quá mạnh mẽ trong tôi. Tôi cần tìm ra cách để vượt qua lo lắng và tìm lại sự tự tin. Sắp tới kì thi, tôi hy vọng có thể kiểm soát được cảm giác lo lắng và trở thành người tự tin hơn.</t>
   </si>
   <si>
     <t>llama-3-8b-instruct-1-24ee2f1342</t>
   </si>
   <si>
     <t>Tôi ngồi yên lặng trong phòng, không thấy hứng thú làm gì. Trông lại những bức tranh cũ, thấy những kỷ niệm buồn. Em của tôi đã qua đời, và tôi không có ai chia sẻ với. Sức khỏe của tôi không ổn, cảm thấy mệt mỏi và chán nản. Không biết tôi sẽ sống bao lâu nữa.
-Mọi việc lại trở lại giống như cũ, nhưng tôi không có thể nào quên được. Em của tôi đã chết, và tôi không thể nào chia sẻ với ai. Sức khỏe của tôi không ổn, và tôi cảm thấy mệt mỏi và chán nản. Tôi không biết tôi sẽ sống bao lâu nữa. Cảm thấy rất buồn, rất nhớ em.</t>
+ Mọi việc lại trở lại giống như cũ, nhưng tôi không có thể nào quên được. Em của tôi đã chết, và tôi không thể nào chia sẻ với ai. Sức khỏe của tôi không ổn, và tôi cảm thấy mệt mỏi và chán nản. Tôi không biết tôi sẽ sống bao lâu nữa. Cảm thấy rất buồn, rất nhớ em.</t>
   </si>
   <si>
     <t>llama-3-8b-instruct-3-1c6afb8759</t>
@@ -379,8 +413,8 @@
   </si>
   <si>
     <t>Mấy giờ chiều, tôi ngồi yên lặng, không muốn làm gì. Lòng tôi tràn đầy sự thất vọng và buồn. Trải qua một ngày, tôi mới nhận được một tin tưởng, một tin tốt, nhưng nó lại không mang lại cho tôi cảm giác hân hỉ như trước.
-Tâm trí tôi chìm trong đam mê và buồn. Tại sao một điều nhỏ lại có thể làm tôi suy sụp đến thế? Tôi nghĩ về những năm tháng qua, những khó khăn tôi đã vượt qua, và giờ đây tôi lại một lần nữa phải đối mặt với sự thất vọng. Bao nhiêu kỷ niệm và những niềm tin đã được hình thành trong tôi, giờ đây lại bị tan chảy như khói.
-Tôi không thể nào nói ra lời cảm ơn đến ai, vì họ chẳng biết về sự thất vọng và buồn của tôi. Tôi chỉ có thể ngồi yên lặng, để cho những điều đã qua tan chảy trong lòng.</t>
+ Tâm trí tôi chìm trong đam mê và buồn. Tại sao một điều nhỏ lại có thể làm tôi suy sụp đến thế? Tôi nghĩ về những năm tháng qua, những khó khăn tôi đã vượt qua, và giờ đây tôi lại một lần nữa phải đối mặt với sự thất vọng. Bao nhiêu kỷ niệm và những niềm tin đã được hình thành trong tôi, giờ đây lại bị tan chảy như khói.
+ Tôi không thể nào nói ra lời cảm ơn đến ai, vì họ chẳng biết về sự thất vọng và buồn của tôi. Tôi chỉ có thể ngồi yên lặng, để cho những điều đã qua tan chảy trong lòng.</t>
   </si>
   <si>
     <t>qwen3-8b-5-317de8a46a</t>
@@ -405,8 +439,8 @@
   </si>
   <si>
     <t>Tôi ngồi lại sau một ngày thực tập dày dạn. Có lẽ vì thế, tôi đã mệt lúng hơn bình thường. Não tôi cứ bám ép một vấn đề đang giải, nhưng đã khó khăn hơn nhiều so với hôm trước. Có những lúc, tôi nghĩ mình đã cố gắng quá sức, nhưng cuối cùng cũng chỉ là một sự trì hoãn. 
-Chẳng có gì đặc biệt xảy ra trong ngày hôm nay, chỉ một chuỗi những việc quen thuộc. Tôi đi lại trên ghế, tay tôi lại bám vào ghế, như thể tôi đang cố níng lại thứ gì đó. 
-Vừa đủ để tôi vào giấc ngủ, không hỏi ai, chỉ để tôi có thể vượt qua một ngày nữa.</t>
+ Chẳng có gì đặc biệt xảy ra trong ngày hôm nay, chỉ một chuỗi những việc quen thuộc. Tôi đi lại trên ghế, tay tôi lại bám vào ghế, như thể tôi đang cố níng lại thứ gì đó. 
+ Vừa đủ để tôi vào giấc ngủ, không hỏi ai, chỉ để tôi có thể vượt qua một ngày nữa.</t>
   </si>
   <si>
     <t>llama-3-8b-instruct-6-3a101218bd</t>
@@ -455,9 +489,9 @@
   </si>
   <si>
     <t>Tôi ngồi trong phòng học, xung quanh là những tờ vở trắng, những câu hỏi và những bài tập. Có vẻ như những giờ học đã gần kết thúc, nhưng tôi vẫn không thể rời khỏi bàn học. Chuyện này có vẻ như là một trò chơi của đầu óc. Tôi chẳng thể nào tập trung, cứ thay đổi chỗ ngồi, rồi lại quay trở lại chỗ cũ. Đừng hỏi ai, tôi chỉ biết là mình đang trong một trạng thái "other".
-Tôi chẳng thể nào tập trung, tôi chẳng thể nào làm bất cứ điều gì. Có vẻ như cuộc sống của tôi đã trở thành một giấc mơ. Tôi chẳng thể nào chia sẻ với ai, tôi chẳng thể nào nói với ai. Tôi chỉ biết là mình đang trong một trạng thái "other". 
-Tôi nhớ một ngày xưa, tôi từng có một cuốn sách yêu thích. Bây giờ, tôi chẳng thể nào nhớ tên sách đó. Có vẻ như tôi đã quên. Tôi không thể nào tìm thấy nó, tôi không thể nào tìm thấy chính mình. 
-Tôi chẳng thể nào làm gì, tôi chẳng thể nào nói gì. Tôi chỉ biết là mình đang trong một trạng thái "other".</t>
+ Tôi chẳng thể nào tập trung, tôi chẳng thể nào làm bất cứ điều gì. Có vẻ như cuộc sống của tôi đã trở thành một giấc mơ. Tôi chẳng thể nào chia sẻ với ai, tôi chẳng thể nào nói với ai. Tôi chỉ biết là mình đang trong một trạng thái "other". 
+ Tôi nhớ một ngày xưa, tôi từng có một cuốn sách yêu thích. Bây giờ, tôi chẳng thể nào nhớ tên sách đó. Có vẻ như tôi đã quên. Tôi không thể nào tìm thấy nó, tôi không thể nào tìm thấy chính mình. 
+ Tôi chẳng thể nào làm gì, tôi chẳng thể nào nói gì. Tôi chỉ biết là mình đang trong một trạng thái "other".</t>
   </si>
   <si>
     <t>llama-3-8b-instruct-1-b515119de4</t>
@@ -548,8 +582,8 @@
   </si>
   <si>
     <t>Hôm nay, tôi và nhóm bạn đã đi ăn tối nhau. Có lẽ, điều đó có thể xem là một điều bình thường, nhưng tôi cảm thấy vô cùng vui vẻ. Chúng ta ngồi lấy nhau, chuyện trò cười đến tận giờ đóng. Tới lúc tôi về nhà, tôi cảm thấy người nhẹ hơn, như thể mình được đổ bỏ hết những căng thẳng.
-Tin ý nghĩ, chúng ta chuyện trò về những điều đã qua, những dự định tương lai, và những thứ khác nữa. Tôi rất thích những lúc như thế. Thật sự, tôi cảm thấy mình được sống trong khoảnh khắc đó, không có gì để lo lắng.
-Tối nay, tôi quay lại nhà với một niềm vui vô cùng. Thật ra, tôi không thể tin mình đã sống một ngày như vậy.</t>
+ Tin ý nghĩ, chúng ta chuyện trò về những điều đã qua, những dự định tương lai, và những thứ khác nữa. Tôi rất thích những lúc như thế. Thật sự, tôi cảm thấy mình được sống trong khoảnh khắc đó, không có gì để lo lắng.
+ Tối nay, tôi quay lại nhà với một niềm vui vô cùng. Thật ra, tôi không thể tin mình đã sống một ngày như vậy.</t>
   </si>
   <si>
     <t>qwen3-8b-2-97e59f2645</t>
@@ -574,7 +608,7 @@
   </si>
   <si>
     <t>Cả ngày qua đi, không có điều gì đặc biệt xảy ra. Nhưng tôi nhớ lại một khoảnh khắc, một chút niềm vui nhỏ, khi tôi hoàn thành công việc hôm nay. Tuy nhiên, niềm vui đó không kéo dài, tôi lại cảm thấy buồn, như thể niềm vui đó là một ảo tưởng.
-Tôi ngồi yên một chỗ, suy nghĩ về những điều có thể khác, về những điều tôi có thể làm khác. Nhưng rồi tôi lại nhớ lại những điều đã qua, những điều đã làm. Mối lo và lo lắng lại quay trở lại. Tôi không thể hiểu tại sao tôi lại buồn đến như vậy. Dường như tôi đã thay đổi, nhưng lại không thay đổi. Tôi không biết nên làm gì.</t>
+ Tôi ngồi yên một chỗ, suy nghĩ về những điều có thể khác, về những điều tôi có thể làm khác. Nhưng rồi tôi lại nhớ lại những điều đã qua, những điều đã làm. Mối lo và lo lắng lại quay trở lại. Tôi không thể hiểu tại sao tôi lại buồn đến như vậy. Dường như tôi đã thay đổi, nhưng lại không thay đổi. Tôi không biết nên làm gì.</t>
   </si>
   <si>
     <t>qwen3-8b-0-08deb9d24f</t>
@@ -587,7 +621,7 @@
   </si>
   <si>
     <t>Tôi ngồi tại bàn học, tay tay cầm bút, cố gắng tập làm việc, nhưng cảm giác trong tôi cứ bồn chồn, ngột ngạt. Tất cả vì một việc nhỏ, nhưng lại là một vấn đề lớn với tôi. Người khác không hiểu, không đồng ý với tôi, cứ như thể tôi không có tiếng nói. Tôi cảm thấy giận, giận như nước bão, giận đến nỗi tôi thậm chí không thể ngồi yên.
-Mình tưởng tượng những lúc như thế, mình sẽ chẳng có ý định làm gì, chỉ nằm im, im như một đống cỏ. Nhưng nay, mình lại phải tiếp tục làm việc, phải tìm cách giải quyết vấn đề này. Mình biết mình không thể ngồi yên, nhưng mình lại không thể chịu thêm nữa. Mình muốn hét, hét cho đến khi người khác lắng tai nghe, nhưng mình lại không dám. Mình chỉ có thể ngồi đây, tay tay cầm bút, chờ đến khi mình tìm cách giải quyết vấn đề này.</t>
+ Mình tưởng tượng những lúc như thế, mình sẽ chẳng có ý định làm gì, chỉ nằm im, im như một đống cỏ. Nhưng nay, mình lại phải tiếp tục làm việc, phải tìm cách giải quyết vấn đề này. Mình biết mình không thể ngồi yên, nhưng mình lại không thể chịu thêm nữa. Mình muốn hét, hét cho đến khi người khác lắng tai nghe, nhưng mình lại không dám. Mình chỉ có thể ngồi đây, tay tay cầm bút, chờ đến khi mình tìm cách giải quyết vấn đề này.</t>
   </si>
   <si>
     <t>qwen3-8b-6-b270b1cb01</t>
@@ -666,8 +700,8 @@
   </si>
   <si>
     <t>Tôi đã thức dậy với một tâm trạng lo lắng và phiền phức. Nghiệp về ngày mai, tôi nghĩ đến những khó khăn và thách thức đang chờ tôi. Tôi sợ mình không chuẩn bị tốt, sợ rằng mọi thứ sẽ vượt ngoài tầm kiểm soát. Điểm ấy làm cho tôi đau đầu và lo lắng, như thể tôi đang bị quăng vào trong một vực sâu không có lối thoát. 
-Tôi đã cố gắng suy nghĩ và tìm kiếm một lối thoát, nhưng điều đó lại khiến tôi lo hơn. Tôi không biết mình nên làm gì, và điều đó làm cho tôi cảm thấy chán nản và hoảng loạn. 
-Cảm giác lo lắng này đã trở thành một phần của tôi, và tôi không thể thoát ra khỏi nó. Tôi chỉ có thể ngồi yên, ngắm nhìn và chờ đợi.</t>
+ Tôi đã cố gắng suy nghĩ và tìm kiếm một lối thoát, nhưng điều đó lại khiến tôi lo hơn. Tôi không biết mình nên làm gì, và điều đó làm cho tôi cảm thấy chán nản và hoảng loạn. 
+ Cảm giác lo lắng này đã trở thành một phần của tôi, và tôi không thể thoát ra khỏi nó. Tôi chỉ có thể ngồi yên, ngắm nhìn và chờ đợi.</t>
   </si>
   <si>
     <t>llama-3-8b-instruct-0-364902c8f8</t>
@@ -710,7 +744,7 @@
   </si>
   <si>
     <t>Tôi thực sự bị giận một cách mãi mãi vì sao người ta lại không tin vào những điều mình nói. Có khi nào họ hỏi tôi về bệnh tật, tôi sẽ nói ra một cáchstraightforward, nhưng họ lại cứ thế, như thể tôi nói không có nghĩa gì. Tôi tưởng tượng ra họ hỏi tôi "Tại sao anh lại bị ốm vậy?" và tôi sẽ trả lời "Vì tôi không運動, không ăn ngon, không ngủ đủ giấc", nhưng họ lại cứ thế, không muốn tin.
-Tất nhiên, sau này tôi có thể sẽ tìm ra cách nói khác, nhưng lúc này, tôi chỉ muốn phàn phàn và than phiền. Tôi thậm chí không muốn ai khác biết điều này, chỉ muốn đóng sầm cửa lại, ngồi im một lúc và hà hỏa. Cái gì nữa, người ta lại hỏi tôi nữa? Xin cho tôi một chút hòa bình!</t>
+ Tất nhiên, sau này tôi có thể sẽ tìm ra cách nói khác, nhưng lúc này, tôi chỉ muốn phàn phàn và than phiền. Tôi thậm chí không muốn ai khác biết điều này, chỉ muốn đóng sầm cửa lại, ngồi im một lúc và hà hỏa. Cái gì nữa, người ta lại hỏi tôi nữa? Xin cho tôi một chút hòa bình!</t>
   </si>
   <si>
     <t>qwen3-8b-3-01aab0098b</t>
@@ -753,14 +787,14 @@
   </si>
   <si>
     <t>Tôi ngồi im lặng, nghĩ về những ngày xưa với anh. Lúc nào anh và tôi có thể ngồi bên nhau, chia sẻ giấc mơ, chia sẻ nỗi sợ. Bây giờ, anh lại đi và tôi lại ngồi đây, nhớ anh như thể hôm qua. Sầu não me lên, không biết tại sao lại hình thành.
-Tôi có thể nhớ những ngày anh còn ở cạnh tôi, chúng ta có thể nói nhiều về tương lai, về ước mơ, về nỗi lo. Bây giờ, anh đã không còn và tôi lại thấy mình bị vứt bỏ. Tựa như tờ giấy trắng, tôi lại phải viết lại câu chuyện của tôi. Chứ sao anh lại đi và tôi lại lại nhớ anh.</t>
+ Tôi có thể nhớ những ngày anh còn ở cạnh tôi, chúng ta có thể nói nhiều về tương lai, về ước mơ, về nỗi lo. Bây giờ, anh đã không còn và tôi lại thấy mình bị vứt bỏ. Tựa như tờ giấy trắng, tôi lại phải viết lại câu chuyện của tôi. Chứ sao anh lại đi và tôi lại lại nhớ anh.</t>
   </si>
   <si>
     <t>llama-3-8b-instruct-0-2d015c8d17</t>
   </si>
   <si>
     <t>Hôm nay, khi vừa rời khỏi quán cà phê, tôi có cảm giác vô cùng thoải mái. Cô gái tôi và tôi có một bữa tiệc dài đến chiều, chia sẻ những điều về cuộc sống, mơ ước, và cả những kinh nghiệm khó khăn. Tôi cảm thấy như mình được giải thoát khỏi những phiền toái, những lo lắng và những phiền hứng. Cũng có những lúc chúng tôi chia sẻ về những điều đau lòng, về những mất mát và những chia tay. Tuy nhiên, ngay sau đó, chúng tôi lại cười, lại chia sẻ, lại sống.
-Tôi được những điều đó làm tôi nhớ lại những khoảnh khắc khó quên, những khoảnh khắc chúng tôi đã chia sẻ với nhau. Được chia sẻ những điều sâu sắc với người khác, được nghe người khác chia sẻ những điều sâu sắc với mình, có thể là một trong những điều đẹp nhất trong cuộc sống. Hôm nay, tôi có thể nói rằng, tôi đã được chia sẻ những điều sâu sắc với cô gái tôi, và đó là một điều rất đặc biệt.</t>
+ Tôi được những điều đó làm tôi nhớ lại những khoảnh khắc khó quên, những khoảnh khắc chúng tôi đã chia sẻ với nhau. Được chia sẻ những điều sâu sắc với người khác, được nghe người khác chia sẻ những điều sâu sắc với mình, có thể là một trong những điều đẹp nhất trong cuộc sống. Hôm nay, tôi có thể nói rằng, tôi đã được chia sẻ những điều sâu sắc với cô gái tôi, và đó là một điều rất đặc biệt.</t>
   </si>
   <si>
     <t>llama-3-8b-instruct-1-d9e62ad602</t>
@@ -851,7 +885,7 @@
   </si>
   <si>
     <t>Tôi ngồi học đến chiều, nhưng không thể tập trung được. Mọi thứ cứ quay quanh trong đầu, những con số và vấn đề, như một cơn sóng đẩy tôi đi. Tôi nhìn ra ngoài cửa, thấy người khác enjoying their free time, không có một chút lo lắng, tôi cảm thấy buồn hơn.
-Mà tôi lại nhớ lại chuyện lúc sáng, khi tôi phải lên trường để làm những bài tập, và giờ đã tới chiều, tôi còn làm rất ít. Tôi không biết vì sao, cảm thấy như thế nào, nhưng cứ ngồi đó, không dám để người khác biết. Buồn. Tạm lặng.</t>
+ Mà tôi lại nhớ lại chuyện lúc sáng, khi tôi phải lên trường để làm những bài tập, và giờ đã tới chiều, tôi còn làm rất ít. Tôi không biết vì sao, cảm thấy như thế nào, nhưng cứ ngồi đó, không dám để người khác biết. Buồn. Tạm lặng.</t>
   </si>
   <si>
     <t>llama-3-8b-instruct-3-3e168df4c9</t>
@@ -882,7 +916,7 @@
   </si>
   <si>
     <t>Cả ngày vừa qua, tôi mới có một thành công nhỏ. Em được công ty phê duyệt một đề án kinh doanh mới. Nhưng cái cảm xúc trong tôi không bằng như những người khác. Tôi không thể cảm nhận hạnh phúc, chỉ cảm thấy buồn.
-Nghiệp xong, tôi ngồi lại nhà, nhìn quanh và nghĩ lại chuyện lúc sáng. Tôi nhớ lại những ngày học, những khó khăn, những đêm tỉnh. Tất cả những khó khăn đã qua, giờ tôi mới có một thành công. Nhưng lại không thấy hạnh phúc. Cảm giác buồn cứ đeo mặt.</t>
+ Nghiệp xong, tôi ngồi lại nhà, nhìn quanh và nghĩ lại chuyện lúc sáng. Tôi nhớ lại những ngày học, những khó khăn, những đêm tỉnh. Tất cả những khó khăn đã qua, giờ tôi mới có một thành công. Nhưng lại không thấy hạnh phúc. Cảm giác buồn cứ đeo mặt.</t>
   </si>
   <si>
     <t>qwen3-8b-6-6cdd0bf252</t>
@@ -895,13 +929,13 @@
   </si>
   <si>
     <t>Mưa hôm qua tôi tham gia một buổi thực tập tại công ty, để cải thiện kỹ năng tiếng Anh. Tôi dự định sẽ tham gia với một nhóm người khác, nhưng khi đến nơi, tôi thấy toàn bộ nhóm những người này ngồi quanh một bàn với vẻ mặt sững sình. Tôi không hiểu sao họ lại làm chuyện đó được. Họ ngồi nhìn người khác, chứ không làm gì cả, và cả nhóm không có nói gì với nhau. Tôi cảm thấy ghê, chỉ muốn chạy đi ngay lập tức.
-Tôi không thể hiểu sao họ lại có thể ngồi yên đó được, khi có thể làm nhiều chuyện khác hơn. Tôi thấy phiền toái và chán nản. Buổi thực tập của tôi đã trở thành một kinh nghiệm khó khăn.</t>
+ Tôi không thể hiểu sao họ lại có thể ngồi yên đó được, khi có thể làm nhiều chuyện khác hơn. Tôi thấy phiền toái và chán nản. Buổi thực tập của tôi đã trở thành một kinh nghiệm khó khăn.</t>
   </si>
   <si>
     <t>llama-3-8b-instruct-6-f15e0275fc</t>
   </si>
   <si>
-    <t>Tôi đi khám bệnh chiều nay và nghe bác sĩ nói rằng tôi bị viêm phổi. Tôi không hiểu sao mình lại bị như vậy, thậm chí tôi còn chán đến mức không muốn đi khám bệnh nữa. Nhưng sau khi được giải quyết xong, tôi lại cảm thấy hơi buồn và lo lắng. Đừng như thế, mình sẽ phải chịu đau  trong một tuần nữa.</t>
+    <t>Tôi đi khám bệnh chiều nay và nghe bác sĩ nói rằng tôi bị viêm phổi. Tôi không hiểu sao mình lại bị như vậy, thậm chí tôi còn chán đến mức không muốn đi khám bệnh nữa. Nhưng sau khi được giải quyết xong, tôi lại cảm thấy hơi buồn và lo lắng. Đừng như thế, mình sẽ phải chịu đau trong một tuần nữa.</t>
   </si>
   <si>
     <t>llama-3-8b-instruct-4-2967520737</t>
@@ -938,7 +972,7 @@
   </si>
   <si>
     <t>Tôi đang ngồi ở nhà, không hiểu sao thời tiết hôm nay lại tồi tệ đến thế. Mưa rào vào như thế, ngô ngô nước đến ngã ngã. Tôi thật khinh ghê vì cái ngày này, chỉ muốn ở trong nhà và xem phim thôi.
-Tâm trạng tôi thật tồi tệ, không hiểu sao người ta có thể xem mặt trời với nắng rào như vậy. Tôi chỉ muốn ẩn mặt, tránh mặt trời và những cơn mưa rào ghê rợ. Ngô ngô, tôi cảm thấy như thế, ghê và buồn.</t>
+ Tâm trạng tôi thật tồi tệ, không hiểu sao người ta có thể xem mặt trời với nắng rào như vậy. Tôi chỉ muốn ẩn mặt, tránh mặt trời và những cơn mưa rào ghê rợ. Ngô ngô, tôi cảm thấy như thế, ghê và buồn.</t>
   </si>
   <si>
     <t>llama-3-8b-instruct-1-7a4ef81d26</t>
@@ -963,7 +997,7 @@
   </si>
   <si>
     <t>Chính từ hôm qua, tôi lại phải trải qua một ngày nữa với sự lo lắng về tiền. Chi tiêu quá nhiều, thu nhập lại quá thấp. Cảm giác chán ngã, như mình đã bị vây bắt trong một vòng luân.
-Tối hôm nay, tôi ngồi trên ghế, không muốn làm gì, chỉ nghĩ lại chuyện cũ. Nỗi lo về tiền cứ ngốn trong đầu, không cho tôi yên.</t>
+ Tối hôm nay, tôi ngồi trên ghế, không muốn làm gì, chỉ nghĩ lại chuyện cũ. Nỗi lo về tiền cứ ngốn trong đầu, không cho tôi yên.</t>
   </si>
   <si>
     <t>llama-3-8b-instruct-0-309efff2ee</t>
@@ -1108,7 +1142,7 @@
   </si>
   <si>
     <t>Hôm nay, tôi thực tập lại với một người đồng nghiệp mới. Tôi chưa từng thấy người này trước, nhưng tôi nghe đã có tiếng về người này là một chuyên gia trong lĩnh vực của tôi. Khi chúng tôi ngồi xuống để thảo luận về công việc, tôi vô cùng bất ngờ. Người này hoàn toàn không có chút chuyên môn, thậm chí không có chút hiểu biết về lĩnh vực này. Tôi cảm thấy vô lực, ngã ngã và thậm chí ghê cả người.
-Tôi không hiểu sao người ta có thể coi mình là một chuyên gia trong lĩnh vực này. Tôi nghĩ rằng người này chỉ đơn giản là người quen biết, không có chút kinh nghiệm hay kiến thức về lĩnh vực này. Tôi cảm thấy vô cùng thất vọng, nghĩ rằng mình đã bị lừa. Tôi không thể tin rằng người này có thể được coi là một chuyên gia. Tôi cảm thấy như thể mình đang ở trong một thế giới khác, xa xa xa so với cái thế giới thực sự.</t>
+ Tôi không hiểu sao người ta có thể coi mình là một chuyên gia trong lĩnh vực này. Tôi nghĩ rằng người này chỉ đơn giản là người quen biết, không có chút kinh nghiệm hay kiến thức về lĩnh vực này. Tôi cảm thấy vô cùng thất vọng, nghĩ rằng mình đã bị lừa. Tôi không thể tin rằng người này có thể được coi là một chuyên gia. Tôi cảm thấy như thể mình đang ở trong một thế giới khác, xa xa xa so với cái thế giới thực sự.</t>
   </si>
   <si>
     <t>qwen3-8b-0-01df33efae</t>
@@ -1145,12 +1179,28 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;Times New Roman&quot;"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;Times New Roman&quot;"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1174,14 +1224,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1194,114 +1259,56 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Sheets">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4285F4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="EA4335"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="FBBC04"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="34A853"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="FF6D01"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="46BDC6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="1155CC"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="1155CC"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1313,160 +1320,131 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1478,1464 +1456,5289 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C181"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:C1000"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="255.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="71.73046875" customWidth="1"/>
+    <col min="3" max="3" width="15.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="35" spans="1:3">
+      <c r="A35" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>55</v>
-      </c>
-      <c r="B28" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>57</v>
-      </c>
-      <c r="B29" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>59</v>
-      </c>
-      <c r="B30" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
-        <v>61</v>
-      </c>
-      <c r="B31" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
-        <v>63</v>
-      </c>
-      <c r="B32" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
-        <v>65</v>
-      </c>
-      <c r="B33" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
-        <v>67</v>
-      </c>
-      <c r="B34" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
-        <v>71</v>
-      </c>
-      <c r="B36" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
-        <v>73</v>
-      </c>
-      <c r="B37" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
-        <v>75</v>
-      </c>
-      <c r="B38" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A39" t="s">
-        <v>77</v>
-      </c>
-      <c r="B39" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A40" t="s">
-        <v>79</v>
-      </c>
-      <c r="B40" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A41" t="s">
-        <v>81</v>
-      </c>
-      <c r="B41" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A42" t="s">
-        <v>83</v>
-      </c>
-      <c r="B42" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A43" t="s">
-        <v>85</v>
-      </c>
-      <c r="B43" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A44" t="s">
-        <v>87</v>
-      </c>
-      <c r="B44" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A45" t="s">
-        <v>89</v>
-      </c>
-      <c r="B45" t="s">
+    <row r="42" spans="1:3">
+      <c r="A42" s="3" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A46" t="s">
+      <c r="B42" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C42" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="3" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A47" t="s">
+      <c r="B43" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C43" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="3" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A48" t="s">
+      <c r="B44" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C44" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A49" t="s">
+      <c r="B45" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C45" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A50" t="s">
+      <c r="B46" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C46" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="3" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A51" t="s">
+      <c r="B47" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C47" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="3" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A52" t="s">
+      <c r="B48" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C48" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A53" t="s">
+      <c r="B49" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C49" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="3" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A54" t="s">
+      <c r="B50" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C50" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="3" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A55" t="s">
+      <c r="B51" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C51" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="3" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A56" t="s">
+      <c r="B52" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C52" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="3" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A57" t="s">
+      <c r="B53" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C53" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="3" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A58" t="s">
+      <c r="B54" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C54" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A59" t="s">
+      <c r="B55" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C55" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="3" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A60" t="s">
+      <c r="B56" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C56" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="3" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A61" t="s">
+      <c r="B57" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C57" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="3" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A62" t="s">
+      <c r="B58" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C58" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="3" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A63" t="s">
+      <c r="B59" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C59" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="3" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A64" t="s">
+      <c r="B60" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C60" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="3" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A65" t="s">
+      <c r="B61" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C61" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="3" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A66" t="s">
+      <c r="B62" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C62" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="3" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A67" t="s">
+      <c r="B63" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C63" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="3" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A68" t="s">
+      <c r="B64" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C64" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="3" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A69" t="s">
+      <c r="B65" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C65" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="3" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A70" t="s">
+      <c r="B66" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C66" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="3" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A71" t="s">
+      <c r="B67" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C67" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="3" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A72" t="s">
+      <c r="B68" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C68" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="3" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A73" t="s">
+      <c r="B69" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C69" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="3" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A74" t="s">
+      <c r="B70" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C70" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="3" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A75" t="s">
+      <c r="B71" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C71" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" s="3" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A76" t="s">
+      <c r="B72" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C72" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="3" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A77" t="s">
+      <c r="B73" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C73" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" s="3" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A78" t="s">
+      <c r="B74" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C74" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="3" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A79" t="s">
+      <c r="B75" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C75" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="3" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A80" t="s">
+      <c r="B76" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C76" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" s="3" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A81" t="s">
+      <c r="B77" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C77" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" s="3" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A82" t="s">
+      <c r="B78" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C78" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" s="3" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A83" t="s">
+      <c r="B79" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C79" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="3" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A84" t="s">
+      <c r="B80" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C80" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="3" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A85" t="s">
+      <c r="B81" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C81" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="3" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A86" t="s">
+      <c r="B82" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C82" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" s="3" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A87" t="s">
+      <c r="B83" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C83" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" s="3" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A88" t="s">
+      <c r="B84" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C84" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" s="3" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A89" t="s">
+      <c r="B85" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C85" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" s="3" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A90" t="s">
+      <c r="B86" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C86" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" s="3" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A91" t="s">
+      <c r="B87" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C87" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" s="3" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A92" t="s">
+      <c r="B88" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C88" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" s="3" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A93" t="s">
+      <c r="B89" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B93" t="s">
+      <c r="C89" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="3" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A94" t="s">
+      <c r="B90" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B94" t="s">
+      <c r="C90" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" s="3" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A95" t="s">
+      <c r="B91" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B95" t="s">
+      <c r="C91" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="3" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A96" t="s">
+      <c r="B92" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="B96" t="s">
+      <c r="C92" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" s="3" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A97" t="s">
+      <c r="B93" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C93" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="3" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A98" t="s">
+      <c r="B94" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B98" t="s">
+      <c r="C94" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" s="3" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A99" t="s">
+      <c r="B95" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C95" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" s="3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A100" t="s">
+      <c r="B96" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B100" t="s">
+      <c r="C96" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="3" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A101" t="s">
+      <c r="B97" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="B101" t="s">
+      <c r="C97" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="3" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A102" t="s">
+      <c r="B98" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C98" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="3" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A103" t="s">
+      <c r="B99" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B103" t="s">
+      <c r="C99" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" s="3" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A104" t="s">
+      <c r="B100" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="B104" t="s">
+      <c r="C100" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" s="3" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A105" t="s">
+      <c r="B101" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B105" t="s">
+      <c r="C101" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" s="3" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A106" t="s">
+      <c r="B102" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B106" t="s">
+      <c r="C102" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" s="3" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A107" t="s">
+      <c r="B103" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="B107" t="s">
+      <c r="C103" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" s="3" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A108" t="s">
+      <c r="B104" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="B108" t="s">
+      <c r="C104" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="3" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A109" t="s">
+      <c r="B105" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="B109" t="s">
+      <c r="C105" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" s="3" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A110" t="s">
+      <c r="B106" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B110" t="s">
+      <c r="C106" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" s="3" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A111" t="s">
+      <c r="B107" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="B111" t="s">
+      <c r="C107" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" s="3" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A112" t="s">
+      <c r="B108" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B112" t="s">
+      <c r="C108" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="3" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A113" t="s">
+      <c r="B109" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="B113" t="s">
+      <c r="C109" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" s="3" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A114" t="s">
+      <c r="B110" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B114" t="s">
+      <c r="C110" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" s="3" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A115" t="s">
+      <c r="B111" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B115" t="s">
+      <c r="C111" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="3" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A116" t="s">
+      <c r="B112" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="B116" t="s">
+      <c r="C112" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="3" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A117" t="s">
+      <c r="B113" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B117" t="s">
+      <c r="C113" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="3" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A118" t="s">
+      <c r="B114" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="B118" t="s">
+      <c r="C114" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" s="3" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A119" t="s">
+      <c r="B115" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B119" t="s">
+      <c r="C115" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" s="3" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A120" t="s">
+      <c r="B116" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B120" t="s">
+      <c r="C116" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" s="3" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A121" t="s">
+      <c r="B117" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B121" t="s">
+      <c r="C117" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" s="3" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A122" t="s">
+      <c r="B118" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="B122" t="s">
+      <c r="C118" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" s="3" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A123" t="s">
+      <c r="B119" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B123" t="s">
+      <c r="C119" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" s="3" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A124" t="s">
+      <c r="B120" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="B124" t="s">
+      <c r="C120" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" s="3" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A125" t="s">
+      <c r="B121" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="B125" t="s">
+      <c r="C121" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" s="3" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A126" t="s">
+      <c r="B122" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="B126" t="s">
+      <c r="C122" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" s="3" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A127" t="s">
+      <c r="B123" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B127" t="s">
+      <c r="C123" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" s="3" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A128" t="s">
+      <c r="B124" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="B128" t="s">
+      <c r="C124" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" s="3" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A129" t="s">
+      <c r="B125" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="B129" t="s">
+      <c r="C125" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" s="3" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A130" t="s">
+      <c r="B126" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B130" t="s">
+      <c r="C126" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" s="3" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A131" t="s">
+      <c r="B127" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="B131" t="s">
+      <c r="C127" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" s="3" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A132" t="s">
+      <c r="B128" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="B132" t="s">
+      <c r="C128" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" s="3" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A133" t="s">
+      <c r="B129" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="B133" t="s">
+      <c r="C129" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" s="3" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A134" t="s">
+      <c r="B130" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="B134" t="s">
+      <c r="C130" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" s="3" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A135" t="s">
+      <c r="B131" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="B135" t="s">
+      <c r="C131" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" s="3" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A136" t="s">
+      <c r="B132" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="B136" t="s">
+      <c r="C132" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" s="3" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A137" t="s">
+      <c r="B133" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="B137" t="s">
+      <c r="C133" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" s="3" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A138" t="s">
+      <c r="B134" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="B138" t="s">
+      <c r="C134" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135" s="3" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A139" t="s">
+      <c r="B135" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="B139" t="s">
+      <c r="C135" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136" s="3" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A140" t="s">
+      <c r="B136" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="B140" t="s">
+      <c r="C136" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137" s="3" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A141" t="s">
+      <c r="B137" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="B141" t="s">
+      <c r="C137" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138" s="3" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A142" t="s">
+      <c r="B138" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="B142" t="s">
+      <c r="C138" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" s="3" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A143" t="s">
+      <c r="B139" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="B143" t="s">
+      <c r="C139" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140" s="3" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A144" t="s">
+      <c r="B140" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="B144" t="s">
+      <c r="C140" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3">
+      <c r="A141" s="3" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A145" t="s">
+      <c r="B141" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="B145" t="s">
+      <c r="C141" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3">
+      <c r="A142" s="3" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A146" t="s">
+      <c r="B142" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="B146" t="s">
+      <c r="C142" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3">
+      <c r="A143" s="3" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A147" t="s">
+      <c r="B143" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="B147" t="s">
+      <c r="C143" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3">
+      <c r="A144" s="3" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A148" t="s">
+      <c r="B144" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="B148" t="s">
+      <c r="C144" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3">
+      <c r="A145" s="3" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A149" t="s">
+      <c r="B145" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="B149" t="s">
+      <c r="C145" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3">
+      <c r="A146" s="3" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A150" t="s">
+      <c r="B146" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="B150" t="s">
+      <c r="C146" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3">
+      <c r="A147" s="3" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A151" t="s">
+      <c r="B147" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="B151" t="s">
+      <c r="C147" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3">
+      <c r="A148" s="3" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A152" t="s">
+      <c r="B148" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="B152" t="s">
+      <c r="C148" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3">
+      <c r="A149" s="3" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A153" t="s">
+      <c r="B149" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="B153" t="s">
+      <c r="C149" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3">
+      <c r="A150" s="3" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A154" t="s">
+      <c r="B150" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="B154" t="s">
+      <c r="C150" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3">
+      <c r="A151" s="3" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A155" t="s">
+      <c r="B151" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="B155" t="s">
+      <c r="C151" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3">
+      <c r="A152" s="3" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A156" t="s">
+      <c r="B152" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="B156" t="s">
+      <c r="C152" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3">
+      <c r="A153" s="3" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A157" t="s">
+      <c r="B153" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="B157" t="s">
+      <c r="C153" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3">
+      <c r="A154" s="3" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A158" t="s">
+      <c r="B154" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="B158" t="s">
+      <c r="C154" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3">
+      <c r="A155" s="3" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A159" t="s">
+      <c r="B155" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="B159" t="s">
+      <c r="C155" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3">
+      <c r="A156" s="3" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A160" t="s">
+      <c r="B156" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="B160" t="s">
+      <c r="C156" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3">
+      <c r="A157" s="3" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A161" t="s">
+      <c r="B157" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="B161" t="s">
+      <c r="C157" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3">
+      <c r="A158" s="3" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A162" t="s">
+      <c r="B158" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="B162" t="s">
+      <c r="C158" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="A159" s="3" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A163" t="s">
+      <c r="B159" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="B163" t="s">
+      <c r="C159" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3">
+      <c r="A160" s="3" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A164" t="s">
+      <c r="B160" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="B164" t="s">
+      <c r="C160" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3">
+      <c r="A161" s="3" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A165" t="s">
+      <c r="B161" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="B165" t="s">
+      <c r="C161" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3">
+      <c r="A162" s="3" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A166" t="s">
+      <c r="B162" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="B166" t="s">
+      <c r="C162" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3">
+      <c r="A163" s="3" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A167" t="s">
+      <c r="B163" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="B167" t="s">
+      <c r="C163" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3">
+      <c r="A164" s="3" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A168" t="s">
+      <c r="B164" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="B168" t="s">
+      <c r="C164" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3">
+      <c r="A165" s="3" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A169" t="s">
+      <c r="B165" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="B169" t="s">
+      <c r="C165" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3">
+      <c r="A166" s="3" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A170" t="s">
+      <c r="B166" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="B170" t="s">
+      <c r="C166" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3">
+      <c r="A167" s="3" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A171" t="s">
+      <c r="B167" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="B171" t="s">
+      <c r="C167" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3">
+      <c r="A168" s="3" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A172" t="s">
+      <c r="B168" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="B172" t="s">
+      <c r="C168" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3">
+      <c r="A169" s="3" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A173" t="s">
+      <c r="B169" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="B173" t="s">
+      <c r="C169" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3">
+      <c r="A170" s="3" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A174" t="s">
+      <c r="B170" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="B174" t="s">
+      <c r="C170" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3">
+      <c r="A171" s="3" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A175" t="s">
+      <c r="B171" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="B175" t="s">
+      <c r="C171" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3">
+      <c r="A172" s="3" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A176" t="s">
+      <c r="B172" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="B176" t="s">
+      <c r="C172" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3">
+      <c r="A173" s="3" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A177" t="s">
+      <c r="B173" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="B177" t="s">
+      <c r="C173" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3">
+      <c r="A174" s="3" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A178" t="s">
+      <c r="B174" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="B178" t="s">
+      <c r="C174" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3">
+      <c r="A175" s="3" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A179" t="s">
+      <c r="B175" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="B179" t="s">
+      <c r="C175" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3">
+      <c r="A176" s="3" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A180" t="s">
+      <c r="B176" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="B180" t="s">
+      <c r="C176" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3">
+      <c r="A177" s="3" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A181" t="s">
+      <c r="B177" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="B181" t="s">
+      <c r="C177" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3">
+      <c r="A178" s="3" t="s">
         <v>362</v>
       </c>
+      <c r="B178" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3">
+      <c r="A179" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3">
+      <c r="A180" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3">
+      <c r="A181" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3">
+      <c r="A182" s="5"/>
+      <c r="B182" s="5"/>
+    </row>
+    <row r="183" spans="1:3">
+      <c r="A183" s="5"/>
+      <c r="B183" s="5"/>
+    </row>
+    <row r="184" spans="1:3">
+      <c r="A184" s="5"/>
+      <c r="B184" s="5"/>
+    </row>
+    <row r="185" spans="1:3">
+      <c r="A185" s="5"/>
+      <c r="B185" s="5"/>
+    </row>
+    <row r="186" spans="1:3">
+      <c r="A186" s="5"/>
+      <c r="B186" s="5"/>
+    </row>
+    <row r="187" spans="1:3">
+      <c r="A187" s="5"/>
+      <c r="B187" s="5"/>
+    </row>
+    <row r="188" spans="1:3">
+      <c r="A188" s="5"/>
+      <c r="B188" s="5"/>
+    </row>
+    <row r="189" spans="1:3">
+      <c r="A189" s="5"/>
+      <c r="B189" s="5"/>
+    </row>
+    <row r="190" spans="1:3">
+      <c r="A190" s="5"/>
+      <c r="B190" s="5"/>
+    </row>
+    <row r="191" spans="1:3">
+      <c r="A191" s="5"/>
+      <c r="B191" s="5"/>
+    </row>
+    <row r="192" spans="1:3">
+      <c r="A192" s="5"/>
+      <c r="B192" s="5"/>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="5"/>
+      <c r="B193" s="5"/>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" s="5"/>
+      <c r="B194" s="5"/>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" s="5"/>
+      <c r="B195" s="5"/>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" s="5"/>
+      <c r="B196" s="5"/>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" s="5"/>
+      <c r="B197" s="5"/>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="5"/>
+      <c r="B198" s="5"/>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" s="5"/>
+      <c r="B199" s="5"/>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" s="5"/>
+      <c r="B200" s="5"/>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="5"/>
+      <c r="B201" s="5"/>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="5"/>
+      <c r="B202" s="5"/>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" s="5"/>
+      <c r="B203" s="5"/>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" s="5"/>
+      <c r="B204" s="5"/>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" s="5"/>
+      <c r="B205" s="5"/>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" s="5"/>
+      <c r="B206" s="5"/>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" s="5"/>
+      <c r="B207" s="5"/>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" s="5"/>
+      <c r="B208" s="5"/>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" s="5"/>
+      <c r="B209" s="5"/>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" s="5"/>
+      <c r="B210" s="5"/>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" s="5"/>
+      <c r="B211" s="5"/>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" s="5"/>
+      <c r="B212" s="5"/>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" s="5"/>
+      <c r="B213" s="5"/>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" s="5"/>
+      <c r="B214" s="5"/>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" s="5"/>
+      <c r="B215" s="5"/>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" s="5"/>
+      <c r="B216" s="5"/>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" s="5"/>
+      <c r="B217" s="5"/>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" s="5"/>
+      <c r="B218" s="5"/>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" s="5"/>
+      <c r="B219" s="5"/>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" s="5"/>
+      <c r="B220" s="5"/>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" s="5"/>
+      <c r="B221" s="5"/>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" s="5"/>
+      <c r="B222" s="5"/>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" s="5"/>
+      <c r="B223" s="5"/>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" s="5"/>
+      <c r="B224" s="5"/>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" s="5"/>
+      <c r="B225" s="5"/>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" s="5"/>
+      <c r="B226" s="5"/>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" s="5"/>
+      <c r="B227" s="5"/>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" s="5"/>
+      <c r="B228" s="5"/>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" s="5"/>
+      <c r="B229" s="5"/>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" s="5"/>
+      <c r="B230" s="5"/>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" s="5"/>
+      <c r="B231" s="5"/>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" s="5"/>
+      <c r="B232" s="5"/>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" s="5"/>
+      <c r="B233" s="5"/>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" s="5"/>
+      <c r="B234" s="5"/>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" s="5"/>
+      <c r="B235" s="5"/>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" s="5"/>
+      <c r="B236" s="5"/>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" s="5"/>
+      <c r="B237" s="5"/>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" s="5"/>
+      <c r="B238" s="5"/>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" s="5"/>
+      <c r="B239" s="5"/>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" s="5"/>
+      <c r="B240" s="5"/>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241" s="5"/>
+      <c r="B241" s="5"/>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242" s="5"/>
+      <c r="B242" s="5"/>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243" s="5"/>
+      <c r="B243" s="5"/>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244" s="5"/>
+      <c r="B244" s="5"/>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245" s="5"/>
+      <c r="B245" s="5"/>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246" s="5"/>
+      <c r="B246" s="5"/>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247" s="5"/>
+      <c r="B247" s="5"/>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248" s="5"/>
+      <c r="B248" s="5"/>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249" s="5"/>
+      <c r="B249" s="5"/>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250" s="5"/>
+      <c r="B250" s="5"/>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251" s="5"/>
+      <c r="B251" s="5"/>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252" s="5"/>
+      <c r="B252" s="5"/>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253" s="5"/>
+      <c r="B253" s="5"/>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254" s="5"/>
+      <c r="B254" s="5"/>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255" s="5"/>
+      <c r="B255" s="5"/>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256" s="5"/>
+      <c r="B256" s="5"/>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257" s="5"/>
+      <c r="B257" s="5"/>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258" s="5"/>
+      <c r="B258" s="5"/>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" s="5"/>
+      <c r="B259" s="5"/>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" s="5"/>
+      <c r="B260" s="5"/>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261" s="5"/>
+      <c r="B261" s="5"/>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262" s="5"/>
+      <c r="B262" s="5"/>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263" s="5"/>
+      <c r="B263" s="5"/>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264" s="5"/>
+      <c r="B264" s="5"/>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265" s="5"/>
+      <c r="B265" s="5"/>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266" s="5"/>
+      <c r="B266" s="5"/>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267" s="5"/>
+      <c r="B267" s="5"/>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268" s="5"/>
+      <c r="B268" s="5"/>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269" s="5"/>
+      <c r="B269" s="5"/>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270" s="5"/>
+      <c r="B270" s="5"/>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271" s="5"/>
+      <c r="B271" s="5"/>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272" s="5"/>
+      <c r="B272" s="5"/>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273" s="5"/>
+      <c r="B273" s="5"/>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274" s="5"/>
+      <c r="B274" s="5"/>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275" s="5"/>
+      <c r="B275" s="5"/>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276" s="5"/>
+      <c r="B276" s="5"/>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277" s="5"/>
+      <c r="B277" s="5"/>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278" s="5"/>
+      <c r="B278" s="5"/>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279" s="5"/>
+      <c r="B279" s="5"/>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280" s="5"/>
+      <c r="B280" s="5"/>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281" s="5"/>
+      <c r="B281" s="5"/>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282" s="5"/>
+      <c r="B282" s="5"/>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283" s="5"/>
+      <c r="B283" s="5"/>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284" s="5"/>
+      <c r="B284" s="5"/>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285" s="5"/>
+      <c r="B285" s="5"/>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286" s="5"/>
+      <c r="B286" s="5"/>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287" s="5"/>
+      <c r="B287" s="5"/>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288" s="5"/>
+      <c r="B288" s="5"/>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289" s="5"/>
+      <c r="B289" s="5"/>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290" s="5"/>
+      <c r="B290" s="5"/>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291" s="5"/>
+      <c r="B291" s="5"/>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292" s="5"/>
+      <c r="B292" s="5"/>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293" s="5"/>
+      <c r="B293" s="5"/>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294" s="5"/>
+      <c r="B294" s="5"/>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295" s="5"/>
+      <c r="B295" s="5"/>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296" s="5"/>
+      <c r="B296" s="5"/>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297" s="5"/>
+      <c r="B297" s="5"/>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298" s="5"/>
+      <c r="B298" s="5"/>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299" s="5"/>
+      <c r="B299" s="5"/>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300" s="5"/>
+      <c r="B300" s="5"/>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301" s="5"/>
+      <c r="B301" s="5"/>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302" s="5"/>
+      <c r="B302" s="5"/>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303" s="5"/>
+      <c r="B303" s="5"/>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304" s="5"/>
+      <c r="B304" s="5"/>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305" s="5"/>
+      <c r="B305" s="5"/>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306" s="5"/>
+      <c r="B306" s="5"/>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307" s="5"/>
+      <c r="B307" s="5"/>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308" s="5"/>
+      <c r="B308" s="5"/>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309" s="5"/>
+      <c r="B309" s="5"/>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310" s="5"/>
+      <c r="B310" s="5"/>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311" s="5"/>
+      <c r="B311" s="5"/>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312" s="5"/>
+      <c r="B312" s="5"/>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313" s="5"/>
+      <c r="B313" s="5"/>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314" s="5"/>
+      <c r="B314" s="5"/>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315" s="5"/>
+      <c r="B315" s="5"/>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316" s="5"/>
+      <c r="B316" s="5"/>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317" s="5"/>
+      <c r="B317" s="5"/>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318" s="5"/>
+      <c r="B318" s="5"/>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319" s="5"/>
+      <c r="B319" s="5"/>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320" s="5"/>
+      <c r="B320" s="5"/>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321" s="5"/>
+      <c r="B321" s="5"/>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322" s="5"/>
+      <c r="B322" s="5"/>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323" s="5"/>
+      <c r="B323" s="5"/>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324" s="5"/>
+      <c r="B324" s="5"/>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325" s="5"/>
+      <c r="B325" s="5"/>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326" s="5"/>
+      <c r="B326" s="5"/>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327" s="5"/>
+      <c r="B327" s="5"/>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328" s="5"/>
+      <c r="B328" s="5"/>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329" s="5"/>
+      <c r="B329" s="5"/>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330" s="5"/>
+      <c r="B330" s="5"/>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331" s="5"/>
+      <c r="B331" s="5"/>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332" s="5"/>
+      <c r="B332" s="5"/>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333" s="5"/>
+      <c r="B333" s="5"/>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334" s="5"/>
+      <c r="B334" s="5"/>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335" s="5"/>
+      <c r="B335" s="5"/>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336" s="5"/>
+      <c r="B336" s="5"/>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337" s="5"/>
+      <c r="B337" s="5"/>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338" s="5"/>
+      <c r="B338" s="5"/>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339" s="5"/>
+      <c r="B339" s="5"/>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340" s="5"/>
+      <c r="B340" s="5"/>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341" s="5"/>
+      <c r="B341" s="5"/>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342" s="5"/>
+      <c r="B342" s="5"/>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343" s="5"/>
+      <c r="B343" s="5"/>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344" s="5"/>
+      <c r="B344" s="5"/>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345" s="5"/>
+      <c r="B345" s="5"/>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346" s="5"/>
+      <c r="B346" s="5"/>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347" s="5"/>
+      <c r="B347" s="5"/>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348" s="5"/>
+      <c r="B348" s="5"/>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349" s="5"/>
+      <c r="B349" s="5"/>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350" s="5"/>
+      <c r="B350" s="5"/>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351" s="5"/>
+      <c r="B351" s="5"/>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352" s="5"/>
+      <c r="B352" s="5"/>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353" s="5"/>
+      <c r="B353" s="5"/>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354" s="5"/>
+      <c r="B354" s="5"/>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355" s="5"/>
+      <c r="B355" s="5"/>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356" s="5"/>
+      <c r="B356" s="5"/>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357" s="5"/>
+      <c r="B357" s="5"/>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358" s="5"/>
+      <c r="B358" s="5"/>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359" s="5"/>
+      <c r="B359" s="5"/>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360" s="5"/>
+      <c r="B360" s="5"/>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361" s="5"/>
+      <c r="B361" s="5"/>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362" s="5"/>
+      <c r="B362" s="5"/>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363" s="5"/>
+      <c r="B363" s="5"/>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364" s="5"/>
+      <c r="B364" s="5"/>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" s="5"/>
+      <c r="B365" s="5"/>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366" s="5"/>
+      <c r="B366" s="5"/>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" s="5"/>
+      <c r="B367" s="5"/>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" s="5"/>
+      <c r="B368" s="5"/>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369" s="5"/>
+      <c r="B369" s="5"/>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370" s="5"/>
+      <c r="B370" s="5"/>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371" s="5"/>
+      <c r="B371" s="5"/>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372" s="5"/>
+      <c r="B372" s="5"/>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373" s="5"/>
+      <c r="B373" s="5"/>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374" s="5"/>
+      <c r="B374" s="5"/>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375" s="5"/>
+      <c r="B375" s="5"/>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376" s="5"/>
+      <c r="B376" s="5"/>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377" s="5"/>
+      <c r="B377" s="5"/>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378" s="5"/>
+      <c r="B378" s="5"/>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379" s="5"/>
+      <c r="B379" s="5"/>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380" s="5"/>
+      <c r="B380" s="5"/>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381" s="5"/>
+      <c r="B381" s="5"/>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382" s="5"/>
+      <c r="B382" s="5"/>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383" s="5"/>
+      <c r="B383" s="5"/>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384" s="5"/>
+      <c r="B384" s="5"/>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385" s="5"/>
+      <c r="B385" s="5"/>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386" s="5"/>
+      <c r="B386" s="5"/>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387" s="5"/>
+      <c r="B387" s="5"/>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388" s="5"/>
+      <c r="B388" s="5"/>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389" s="5"/>
+      <c r="B389" s="5"/>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390" s="5"/>
+      <c r="B390" s="5"/>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391" s="5"/>
+      <c r="B391" s="5"/>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392" s="5"/>
+      <c r="B392" s="5"/>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393" s="5"/>
+      <c r="B393" s="5"/>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394" s="5"/>
+      <c r="B394" s="5"/>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395" s="5"/>
+      <c r="B395" s="5"/>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396" s="5"/>
+      <c r="B396" s="5"/>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397" s="5"/>
+      <c r="B397" s="5"/>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398" s="5"/>
+      <c r="B398" s="5"/>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399" s="5"/>
+      <c r="B399" s="5"/>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400" s="5"/>
+      <c r="B400" s="5"/>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401" s="5"/>
+      <c r="B401" s="5"/>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402" s="5"/>
+      <c r="B402" s="5"/>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403" s="5"/>
+      <c r="B403" s="5"/>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404" s="5"/>
+      <c r="B404" s="5"/>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405" s="5"/>
+      <c r="B405" s="5"/>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406" s="5"/>
+      <c r="B406" s="5"/>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407" s="5"/>
+      <c r="B407" s="5"/>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408" s="5"/>
+      <c r="B408" s="5"/>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409" s="5"/>
+      <c r="B409" s="5"/>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410" s="5"/>
+      <c r="B410" s="5"/>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411" s="5"/>
+      <c r="B411" s="5"/>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412" s="5"/>
+      <c r="B412" s="5"/>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413" s="5"/>
+      <c r="B413" s="5"/>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414" s="5"/>
+      <c r="B414" s="5"/>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415" s="5"/>
+      <c r="B415" s="5"/>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416" s="5"/>
+      <c r="B416" s="5"/>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417" s="5"/>
+      <c r="B417" s="5"/>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418" s="5"/>
+      <c r="B418" s="5"/>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419" s="5"/>
+      <c r="B419" s="5"/>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420" s="5"/>
+      <c r="B420" s="5"/>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421" s="5"/>
+      <c r="B421" s="5"/>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422" s="5"/>
+      <c r="B422" s="5"/>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423" s="5"/>
+      <c r="B423" s="5"/>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424" s="5"/>
+      <c r="B424" s="5"/>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425" s="5"/>
+      <c r="B425" s="5"/>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426" s="5"/>
+      <c r="B426" s="5"/>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427" s="5"/>
+      <c r="B427" s="5"/>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428" s="5"/>
+      <c r="B428" s="5"/>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429" s="5"/>
+      <c r="B429" s="5"/>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430" s="5"/>
+      <c r="B430" s="5"/>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431" s="5"/>
+      <c r="B431" s="5"/>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432" s="5"/>
+      <c r="B432" s="5"/>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433" s="5"/>
+      <c r="B433" s="5"/>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434" s="5"/>
+      <c r="B434" s="5"/>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435" s="5"/>
+      <c r="B435" s="5"/>
+    </row>
+    <row r="436" spans="1:2">
+      <c r="A436" s="5"/>
+      <c r="B436" s="5"/>
+    </row>
+    <row r="437" spans="1:2">
+      <c r="A437" s="5"/>
+      <c r="B437" s="5"/>
+    </row>
+    <row r="438" spans="1:2">
+      <c r="A438" s="5"/>
+      <c r="B438" s="5"/>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439" s="5"/>
+      <c r="B439" s="5"/>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440" s="5"/>
+      <c r="B440" s="5"/>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441" s="5"/>
+      <c r="B441" s="5"/>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442" s="5"/>
+      <c r="B442" s="5"/>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443" s="5"/>
+      <c r="B443" s="5"/>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444" s="5"/>
+      <c r="B444" s="5"/>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445" s="5"/>
+      <c r="B445" s="5"/>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446" s="5"/>
+      <c r="B446" s="5"/>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447" s="5"/>
+      <c r="B447" s="5"/>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448" s="5"/>
+      <c r="B448" s="5"/>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449" s="5"/>
+      <c r="B449" s="5"/>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450" s="5"/>
+      <c r="B450" s="5"/>
+    </row>
+    <row r="451" spans="1:2">
+      <c r="A451" s="5"/>
+      <c r="B451" s="5"/>
+    </row>
+    <row r="452" spans="1:2">
+      <c r="A452" s="5"/>
+      <c r="B452" s="5"/>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453" s="5"/>
+      <c r="B453" s="5"/>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454" s="5"/>
+      <c r="B454" s="5"/>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455" s="5"/>
+      <c r="B455" s="5"/>
+    </row>
+    <row r="456" spans="1:2">
+      <c r="A456" s="5"/>
+      <c r="B456" s="5"/>
+    </row>
+    <row r="457" spans="1:2">
+      <c r="A457" s="5"/>
+      <c r="B457" s="5"/>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458" s="5"/>
+      <c r="B458" s="5"/>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459" s="5"/>
+      <c r="B459" s="5"/>
+    </row>
+    <row r="460" spans="1:2">
+      <c r="A460" s="5"/>
+      <c r="B460" s="5"/>
+    </row>
+    <row r="461" spans="1:2">
+      <c r="A461" s="5"/>
+      <c r="B461" s="5"/>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462" s="5"/>
+      <c r="B462" s="5"/>
+    </row>
+    <row r="463" spans="1:2">
+      <c r="A463" s="5"/>
+      <c r="B463" s="5"/>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464" s="5"/>
+      <c r="B464" s="5"/>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465" s="5"/>
+      <c r="B465" s="5"/>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466" s="5"/>
+      <c r="B466" s="5"/>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467" s="5"/>
+      <c r="B467" s="5"/>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468" s="5"/>
+      <c r="B468" s="5"/>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469" s="5"/>
+      <c r="B469" s="5"/>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470" s="5"/>
+      <c r="B470" s="5"/>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471" s="5"/>
+      <c r="B471" s="5"/>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472" s="5"/>
+      <c r="B472" s="5"/>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473" s="5"/>
+      <c r="B473" s="5"/>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474" s="5"/>
+      <c r="B474" s="5"/>
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475" s="5"/>
+      <c r="B475" s="5"/>
+    </row>
+    <row r="476" spans="1:2">
+      <c r="A476" s="5"/>
+      <c r="B476" s="5"/>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477" s="5"/>
+      <c r="B477" s="5"/>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478" s="5"/>
+      <c r="B478" s="5"/>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479" s="5"/>
+      <c r="B479" s="5"/>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480" s="5"/>
+      <c r="B480" s="5"/>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481" s="5"/>
+      <c r="B481" s="5"/>
+    </row>
+    <row r="482" spans="1:2">
+      <c r="A482" s="5"/>
+      <c r="B482" s="5"/>
+    </row>
+    <row r="483" spans="1:2">
+      <c r="A483" s="5"/>
+      <c r="B483" s="5"/>
+    </row>
+    <row r="484" spans="1:2">
+      <c r="A484" s="5"/>
+      <c r="B484" s="5"/>
+    </row>
+    <row r="485" spans="1:2">
+      <c r="A485" s="5"/>
+      <c r="B485" s="5"/>
+    </row>
+    <row r="486" spans="1:2">
+      <c r="A486" s="5"/>
+      <c r="B486" s="5"/>
+    </row>
+    <row r="487" spans="1:2">
+      <c r="A487" s="5"/>
+      <c r="B487" s="5"/>
+    </row>
+    <row r="488" spans="1:2">
+      <c r="A488" s="5"/>
+      <c r="B488" s="5"/>
+    </row>
+    <row r="489" spans="1:2">
+      <c r="A489" s="5"/>
+      <c r="B489" s="5"/>
+    </row>
+    <row r="490" spans="1:2">
+      <c r="A490" s="5"/>
+      <c r="B490" s="5"/>
+    </row>
+    <row r="491" spans="1:2">
+      <c r="A491" s="5"/>
+      <c r="B491" s="5"/>
+    </row>
+    <row r="492" spans="1:2">
+      <c r="A492" s="5"/>
+      <c r="B492" s="5"/>
+    </row>
+    <row r="493" spans="1:2">
+      <c r="A493" s="5"/>
+      <c r="B493" s="5"/>
+    </row>
+    <row r="494" spans="1:2">
+      <c r="A494" s="5"/>
+      <c r="B494" s="5"/>
+    </row>
+    <row r="495" spans="1:2">
+      <c r="A495" s="5"/>
+      <c r="B495" s="5"/>
+    </row>
+    <row r="496" spans="1:2">
+      <c r="A496" s="5"/>
+      <c r="B496" s="5"/>
+    </row>
+    <row r="497" spans="1:2">
+      <c r="A497" s="5"/>
+      <c r="B497" s="5"/>
+    </row>
+    <row r="498" spans="1:2">
+      <c r="A498" s="5"/>
+      <c r="B498" s="5"/>
+    </row>
+    <row r="499" spans="1:2">
+      <c r="A499" s="5"/>
+      <c r="B499" s="5"/>
+    </row>
+    <row r="500" spans="1:2">
+      <c r="A500" s="5"/>
+      <c r="B500" s="5"/>
+    </row>
+    <row r="501" spans="1:2">
+      <c r="A501" s="5"/>
+      <c r="B501" s="5"/>
+    </row>
+    <row r="502" spans="1:2">
+      <c r="A502" s="5"/>
+      <c r="B502" s="5"/>
+    </row>
+    <row r="503" spans="1:2">
+      <c r="A503" s="5"/>
+      <c r="B503" s="5"/>
+    </row>
+    <row r="504" spans="1:2">
+      <c r="A504" s="5"/>
+      <c r="B504" s="5"/>
+    </row>
+    <row r="505" spans="1:2">
+      <c r="A505" s="5"/>
+      <c r="B505" s="5"/>
+    </row>
+    <row r="506" spans="1:2">
+      <c r="A506" s="5"/>
+      <c r="B506" s="5"/>
+    </row>
+    <row r="507" spans="1:2">
+      <c r="A507" s="5"/>
+      <c r="B507" s="5"/>
+    </row>
+    <row r="508" spans="1:2">
+      <c r="A508" s="5"/>
+      <c r="B508" s="5"/>
+    </row>
+    <row r="509" spans="1:2">
+      <c r="A509" s="5"/>
+      <c r="B509" s="5"/>
+    </row>
+    <row r="510" spans="1:2">
+      <c r="A510" s="5"/>
+      <c r="B510" s="5"/>
+    </row>
+    <row r="511" spans="1:2">
+      <c r="A511" s="5"/>
+      <c r="B511" s="5"/>
+    </row>
+    <row r="512" spans="1:2">
+      <c r="A512" s="5"/>
+      <c r="B512" s="5"/>
+    </row>
+    <row r="513" spans="1:2">
+      <c r="A513" s="5"/>
+      <c r="B513" s="5"/>
+    </row>
+    <row r="514" spans="1:2">
+      <c r="A514" s="5"/>
+      <c r="B514" s="5"/>
+    </row>
+    <row r="515" spans="1:2">
+      <c r="A515" s="5"/>
+      <c r="B515" s="5"/>
+    </row>
+    <row r="516" spans="1:2">
+      <c r="A516" s="5"/>
+      <c r="B516" s="5"/>
+    </row>
+    <row r="517" spans="1:2">
+      <c r="A517" s="5"/>
+      <c r="B517" s="5"/>
+    </row>
+    <row r="518" spans="1:2">
+      <c r="A518" s="5"/>
+      <c r="B518" s="5"/>
+    </row>
+    <row r="519" spans="1:2">
+      <c r="A519" s="5"/>
+      <c r="B519" s="5"/>
+    </row>
+    <row r="520" spans="1:2">
+      <c r="A520" s="5"/>
+      <c r="B520" s="5"/>
+    </row>
+    <row r="521" spans="1:2">
+      <c r="A521" s="5"/>
+      <c r="B521" s="5"/>
+    </row>
+    <row r="522" spans="1:2">
+      <c r="A522" s="5"/>
+      <c r="B522" s="5"/>
+    </row>
+    <row r="523" spans="1:2">
+      <c r="A523" s="5"/>
+      <c r="B523" s="5"/>
+    </row>
+    <row r="524" spans="1:2">
+      <c r="A524" s="5"/>
+      <c r="B524" s="5"/>
+    </row>
+    <row r="525" spans="1:2">
+      <c r="A525" s="5"/>
+      <c r="B525" s="5"/>
+    </row>
+    <row r="526" spans="1:2">
+      <c r="A526" s="5"/>
+      <c r="B526" s="5"/>
+    </row>
+    <row r="527" spans="1:2">
+      <c r="A527" s="5"/>
+      <c r="B527" s="5"/>
+    </row>
+    <row r="528" spans="1:2">
+      <c r="A528" s="5"/>
+      <c r="B528" s="5"/>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="A529" s="5"/>
+      <c r="B529" s="5"/>
+    </row>
+    <row r="530" spans="1:2">
+      <c r="A530" s="5"/>
+      <c r="B530" s="5"/>
+    </row>
+    <row r="531" spans="1:2">
+      <c r="A531" s="5"/>
+      <c r="B531" s="5"/>
+    </row>
+    <row r="532" spans="1:2">
+      <c r="A532" s="5"/>
+      <c r="B532" s="5"/>
+    </row>
+    <row r="533" spans="1:2">
+      <c r="A533" s="5"/>
+      <c r="B533" s="5"/>
+    </row>
+    <row r="534" spans="1:2">
+      <c r="A534" s="5"/>
+      <c r="B534" s="5"/>
+    </row>
+    <row r="535" spans="1:2">
+      <c r="A535" s="5"/>
+      <c r="B535" s="5"/>
+    </row>
+    <row r="536" spans="1:2">
+      <c r="A536" s="5"/>
+      <c r="B536" s="5"/>
+    </row>
+    <row r="537" spans="1:2">
+      <c r="A537" s="5"/>
+      <c r="B537" s="5"/>
+    </row>
+    <row r="538" spans="1:2">
+      <c r="A538" s="5"/>
+      <c r="B538" s="5"/>
+    </row>
+    <row r="539" spans="1:2">
+      <c r="A539" s="5"/>
+      <c r="B539" s="5"/>
+    </row>
+    <row r="540" spans="1:2">
+      <c r="A540" s="5"/>
+      <c r="B540" s="5"/>
+    </row>
+    <row r="541" spans="1:2">
+      <c r="A541" s="5"/>
+      <c r="B541" s="5"/>
+    </row>
+    <row r="542" spans="1:2">
+      <c r="A542" s="5"/>
+      <c r="B542" s="5"/>
+    </row>
+    <row r="543" spans="1:2">
+      <c r="A543" s="5"/>
+      <c r="B543" s="5"/>
+    </row>
+    <row r="544" spans="1:2">
+      <c r="A544" s="5"/>
+      <c r="B544" s="5"/>
+    </row>
+    <row r="545" spans="1:2">
+      <c r="A545" s="5"/>
+      <c r="B545" s="5"/>
+    </row>
+    <row r="546" spans="1:2">
+      <c r="A546" s="5"/>
+      <c r="B546" s="5"/>
+    </row>
+    <row r="547" spans="1:2">
+      <c r="A547" s="5"/>
+      <c r="B547" s="5"/>
+    </row>
+    <row r="548" spans="1:2">
+      <c r="A548" s="5"/>
+      <c r="B548" s="5"/>
+    </row>
+    <row r="549" spans="1:2">
+      <c r="A549" s="5"/>
+      <c r="B549" s="5"/>
+    </row>
+    <row r="550" spans="1:2">
+      <c r="A550" s="5"/>
+      <c r="B550" s="5"/>
+    </row>
+    <row r="551" spans="1:2">
+      <c r="A551" s="5"/>
+      <c r="B551" s="5"/>
+    </row>
+    <row r="552" spans="1:2">
+      <c r="A552" s="5"/>
+      <c r="B552" s="5"/>
+    </row>
+    <row r="553" spans="1:2">
+      <c r="A553" s="5"/>
+      <c r="B553" s="5"/>
+    </row>
+    <row r="554" spans="1:2">
+      <c r="A554" s="5"/>
+      <c r="B554" s="5"/>
+    </row>
+    <row r="555" spans="1:2">
+      <c r="A555" s="5"/>
+      <c r="B555" s="5"/>
+    </row>
+    <row r="556" spans="1:2">
+      <c r="A556" s="5"/>
+      <c r="B556" s="5"/>
+    </row>
+    <row r="557" spans="1:2">
+      <c r="A557" s="5"/>
+      <c r="B557" s="5"/>
+    </row>
+    <row r="558" spans="1:2">
+      <c r="A558" s="5"/>
+      <c r="B558" s="5"/>
+    </row>
+    <row r="559" spans="1:2">
+      <c r="A559" s="5"/>
+      <c r="B559" s="5"/>
+    </row>
+    <row r="560" spans="1:2">
+      <c r="A560" s="5"/>
+      <c r="B560" s="5"/>
+    </row>
+    <row r="561" spans="1:2">
+      <c r="A561" s="5"/>
+      <c r="B561" s="5"/>
+    </row>
+    <row r="562" spans="1:2">
+      <c r="A562" s="5"/>
+      <c r="B562" s="5"/>
+    </row>
+    <row r="563" spans="1:2">
+      <c r="A563" s="5"/>
+      <c r="B563" s="5"/>
+    </row>
+    <row r="564" spans="1:2">
+      <c r="A564" s="5"/>
+      <c r="B564" s="5"/>
+    </row>
+    <row r="565" spans="1:2">
+      <c r="A565" s="5"/>
+      <c r="B565" s="5"/>
+    </row>
+    <row r="566" spans="1:2">
+      <c r="A566" s="5"/>
+      <c r="B566" s="5"/>
+    </row>
+    <row r="567" spans="1:2">
+      <c r="A567" s="5"/>
+      <c r="B567" s="5"/>
+    </row>
+    <row r="568" spans="1:2">
+      <c r="A568" s="5"/>
+      <c r="B568" s="5"/>
+    </row>
+    <row r="569" spans="1:2">
+      <c r="A569" s="5"/>
+      <c r="B569" s="5"/>
+    </row>
+    <row r="570" spans="1:2">
+      <c r="A570" s="5"/>
+      <c r="B570" s="5"/>
+    </row>
+    <row r="571" spans="1:2">
+      <c r="A571" s="5"/>
+      <c r="B571" s="5"/>
+    </row>
+    <row r="572" spans="1:2">
+      <c r="A572" s="5"/>
+      <c r="B572" s="5"/>
+    </row>
+    <row r="573" spans="1:2">
+      <c r="A573" s="5"/>
+      <c r="B573" s="5"/>
+    </row>
+    <row r="574" spans="1:2">
+      <c r="A574" s="5"/>
+      <c r="B574" s="5"/>
+    </row>
+    <row r="575" spans="1:2">
+      <c r="A575" s="5"/>
+      <c r="B575" s="5"/>
+    </row>
+    <row r="576" spans="1:2">
+      <c r="A576" s="5"/>
+      <c r="B576" s="5"/>
+    </row>
+    <row r="577" spans="1:2">
+      <c r="A577" s="5"/>
+      <c r="B577" s="5"/>
+    </row>
+    <row r="578" spans="1:2">
+      <c r="A578" s="5"/>
+      <c r="B578" s="5"/>
+    </row>
+    <row r="579" spans="1:2">
+      <c r="A579" s="5"/>
+      <c r="B579" s="5"/>
+    </row>
+    <row r="580" spans="1:2">
+      <c r="A580" s="5"/>
+      <c r="B580" s="5"/>
+    </row>
+    <row r="581" spans="1:2">
+      <c r="A581" s="5"/>
+      <c r="B581" s="5"/>
+    </row>
+    <row r="582" spans="1:2">
+      <c r="A582" s="5"/>
+      <c r="B582" s="5"/>
+    </row>
+    <row r="583" spans="1:2">
+      <c r="A583" s="5"/>
+      <c r="B583" s="5"/>
+    </row>
+    <row r="584" spans="1:2">
+      <c r="A584" s="5"/>
+      <c r="B584" s="5"/>
+    </row>
+    <row r="585" spans="1:2">
+      <c r="A585" s="5"/>
+      <c r="B585" s="5"/>
+    </row>
+    <row r="586" spans="1:2">
+      <c r="A586" s="5"/>
+      <c r="B586" s="5"/>
+    </row>
+    <row r="587" spans="1:2">
+      <c r="A587" s="5"/>
+      <c r="B587" s="5"/>
+    </row>
+    <row r="588" spans="1:2">
+      <c r="A588" s="5"/>
+      <c r="B588" s="5"/>
+    </row>
+    <row r="589" spans="1:2">
+      <c r="A589" s="5"/>
+      <c r="B589" s="5"/>
+    </row>
+    <row r="590" spans="1:2">
+      <c r="A590" s="5"/>
+      <c r="B590" s="5"/>
+    </row>
+    <row r="591" spans="1:2">
+      <c r="A591" s="5"/>
+      <c r="B591" s="5"/>
+    </row>
+    <row r="592" spans="1:2">
+      <c r="A592" s="5"/>
+      <c r="B592" s="5"/>
+    </row>
+    <row r="593" spans="1:2">
+      <c r="A593" s="5"/>
+      <c r="B593" s="5"/>
+    </row>
+    <row r="594" spans="1:2">
+      <c r="A594" s="5"/>
+      <c r="B594" s="5"/>
+    </row>
+    <row r="595" spans="1:2">
+      <c r="A595" s="5"/>
+      <c r="B595" s="5"/>
+    </row>
+    <row r="596" spans="1:2">
+      <c r="A596" s="5"/>
+      <c r="B596" s="5"/>
+    </row>
+    <row r="597" spans="1:2">
+      <c r="A597" s="5"/>
+      <c r="B597" s="5"/>
+    </row>
+    <row r="598" spans="1:2">
+      <c r="A598" s="5"/>
+      <c r="B598" s="5"/>
+    </row>
+    <row r="599" spans="1:2">
+      <c r="A599" s="5"/>
+      <c r="B599" s="5"/>
+    </row>
+    <row r="600" spans="1:2">
+      <c r="A600" s="5"/>
+      <c r="B600" s="5"/>
+    </row>
+    <row r="601" spans="1:2">
+      <c r="A601" s="5"/>
+      <c r="B601" s="5"/>
+    </row>
+    <row r="602" spans="1:2">
+      <c r="A602" s="5"/>
+      <c r="B602" s="5"/>
+    </row>
+    <row r="603" spans="1:2">
+      <c r="A603" s="5"/>
+      <c r="B603" s="5"/>
+    </row>
+    <row r="604" spans="1:2">
+      <c r="A604" s="5"/>
+      <c r="B604" s="5"/>
+    </row>
+    <row r="605" spans="1:2">
+      <c r="A605" s="5"/>
+      <c r="B605" s="5"/>
+    </row>
+    <row r="606" spans="1:2">
+      <c r="A606" s="5"/>
+      <c r="B606" s="5"/>
+    </row>
+    <row r="607" spans="1:2">
+      <c r="A607" s="5"/>
+      <c r="B607" s="5"/>
+    </row>
+    <row r="608" spans="1:2">
+      <c r="A608" s="5"/>
+      <c r="B608" s="5"/>
+    </row>
+    <row r="609" spans="1:2">
+      <c r="A609" s="5"/>
+      <c r="B609" s="5"/>
+    </row>
+    <row r="610" spans="1:2">
+      <c r="A610" s="5"/>
+      <c r="B610" s="5"/>
+    </row>
+    <row r="611" spans="1:2">
+      <c r="A611" s="5"/>
+      <c r="B611" s="5"/>
+    </row>
+    <row r="612" spans="1:2">
+      <c r="A612" s="5"/>
+      <c r="B612" s="5"/>
+    </row>
+    <row r="613" spans="1:2">
+      <c r="A613" s="5"/>
+      <c r="B613" s="5"/>
+    </row>
+    <row r="614" spans="1:2">
+      <c r="A614" s="5"/>
+      <c r="B614" s="5"/>
+    </row>
+    <row r="615" spans="1:2">
+      <c r="A615" s="5"/>
+      <c r="B615" s="5"/>
+    </row>
+    <row r="616" spans="1:2">
+      <c r="A616" s="5"/>
+      <c r="B616" s="5"/>
+    </row>
+    <row r="617" spans="1:2">
+      <c r="A617" s="5"/>
+      <c r="B617" s="5"/>
+    </row>
+    <row r="618" spans="1:2">
+      <c r="A618" s="5"/>
+      <c r="B618" s="5"/>
+    </row>
+    <row r="619" spans="1:2">
+      <c r="A619" s="5"/>
+      <c r="B619" s="5"/>
+    </row>
+    <row r="620" spans="1:2">
+      <c r="A620" s="5"/>
+      <c r="B620" s="5"/>
+    </row>
+    <row r="621" spans="1:2">
+      <c r="A621" s="5"/>
+      <c r="B621" s="5"/>
+    </row>
+    <row r="622" spans="1:2">
+      <c r="A622" s="5"/>
+      <c r="B622" s="5"/>
+    </row>
+    <row r="623" spans="1:2">
+      <c r="A623" s="5"/>
+      <c r="B623" s="5"/>
+    </row>
+    <row r="624" spans="1:2">
+      <c r="A624" s="5"/>
+      <c r="B624" s="5"/>
+    </row>
+    <row r="625" spans="1:2">
+      <c r="A625" s="5"/>
+      <c r="B625" s="5"/>
+    </row>
+    <row r="626" spans="1:2">
+      <c r="A626" s="5"/>
+      <c r="B626" s="5"/>
+    </row>
+    <row r="627" spans="1:2">
+      <c r="A627" s="5"/>
+      <c r="B627" s="5"/>
+    </row>
+    <row r="628" spans="1:2">
+      <c r="A628" s="5"/>
+      <c r="B628" s="5"/>
+    </row>
+    <row r="629" spans="1:2">
+      <c r="A629" s="5"/>
+      <c r="B629" s="5"/>
+    </row>
+    <row r="630" spans="1:2">
+      <c r="A630" s="5"/>
+      <c r="B630" s="5"/>
+    </row>
+    <row r="631" spans="1:2">
+      <c r="A631" s="5"/>
+      <c r="B631" s="5"/>
+    </row>
+    <row r="632" spans="1:2">
+      <c r="A632" s="5"/>
+      <c r="B632" s="5"/>
+    </row>
+    <row r="633" spans="1:2">
+      <c r="A633" s="5"/>
+      <c r="B633" s="5"/>
+    </row>
+    <row r="634" spans="1:2">
+      <c r="A634" s="5"/>
+      <c r="B634" s="5"/>
+    </row>
+    <row r="635" spans="1:2">
+      <c r="A635" s="5"/>
+      <c r="B635" s="5"/>
+    </row>
+    <row r="636" spans="1:2">
+      <c r="A636" s="5"/>
+      <c r="B636" s="5"/>
+    </row>
+    <row r="637" spans="1:2">
+      <c r="A637" s="5"/>
+      <c r="B637" s="5"/>
+    </row>
+    <row r="638" spans="1:2">
+      <c r="A638" s="5"/>
+      <c r="B638" s="5"/>
+    </row>
+    <row r="639" spans="1:2">
+      <c r="A639" s="5"/>
+      <c r="B639" s="5"/>
+    </row>
+    <row r="640" spans="1:2">
+      <c r="A640" s="5"/>
+      <c r="B640" s="5"/>
+    </row>
+    <row r="641" spans="1:2">
+      <c r="A641" s="5"/>
+      <c r="B641" s="5"/>
+    </row>
+    <row r="642" spans="1:2">
+      <c r="A642" s="5"/>
+      <c r="B642" s="5"/>
+    </row>
+    <row r="643" spans="1:2">
+      <c r="A643" s="5"/>
+      <c r="B643" s="5"/>
+    </row>
+    <row r="644" spans="1:2">
+      <c r="A644" s="5"/>
+      <c r="B644" s="5"/>
+    </row>
+    <row r="645" spans="1:2">
+      <c r="A645" s="5"/>
+      <c r="B645" s="5"/>
+    </row>
+    <row r="646" spans="1:2">
+      <c r="A646" s="5"/>
+      <c r="B646" s="5"/>
+    </row>
+    <row r="647" spans="1:2">
+      <c r="A647" s="5"/>
+      <c r="B647" s="5"/>
+    </row>
+    <row r="648" spans="1:2">
+      <c r="A648" s="5"/>
+      <c r="B648" s="5"/>
+    </row>
+    <row r="649" spans="1:2">
+      <c r="A649" s="5"/>
+      <c r="B649" s="5"/>
+    </row>
+    <row r="650" spans="1:2">
+      <c r="A650" s="5"/>
+      <c r="B650" s="5"/>
+    </row>
+    <row r="651" spans="1:2">
+      <c r="A651" s="5"/>
+      <c r="B651" s="5"/>
+    </row>
+    <row r="652" spans="1:2">
+      <c r="A652" s="5"/>
+      <c r="B652" s="5"/>
+    </row>
+    <row r="653" spans="1:2">
+      <c r="A653" s="5"/>
+      <c r="B653" s="5"/>
+    </row>
+    <row r="654" spans="1:2">
+      <c r="A654" s="5"/>
+      <c r="B654" s="5"/>
+    </row>
+    <row r="655" spans="1:2">
+      <c r="A655" s="5"/>
+      <c r="B655" s="5"/>
+    </row>
+    <row r="656" spans="1:2">
+      <c r="A656" s="5"/>
+      <c r="B656" s="5"/>
+    </row>
+    <row r="657" spans="1:2">
+      <c r="A657" s="5"/>
+      <c r="B657" s="5"/>
+    </row>
+    <row r="658" spans="1:2">
+      <c r="A658" s="5"/>
+      <c r="B658" s="5"/>
+    </row>
+    <row r="659" spans="1:2">
+      <c r="A659" s="5"/>
+      <c r="B659" s="5"/>
+    </row>
+    <row r="660" spans="1:2">
+      <c r="A660" s="5"/>
+      <c r="B660" s="5"/>
+    </row>
+    <row r="661" spans="1:2">
+      <c r="A661" s="5"/>
+      <c r="B661" s="5"/>
+    </row>
+    <row r="662" spans="1:2">
+      <c r="A662" s="5"/>
+      <c r="B662" s="5"/>
+    </row>
+    <row r="663" spans="1:2">
+      <c r="A663" s="5"/>
+      <c r="B663" s="5"/>
+    </row>
+    <row r="664" spans="1:2">
+      <c r="A664" s="5"/>
+      <c r="B664" s="5"/>
+    </row>
+    <row r="665" spans="1:2">
+      <c r="A665" s="5"/>
+      <c r="B665" s="5"/>
+    </row>
+    <row r="666" spans="1:2">
+      <c r="A666" s="5"/>
+      <c r="B666" s="5"/>
+    </row>
+    <row r="667" spans="1:2">
+      <c r="A667" s="5"/>
+      <c r="B667" s="5"/>
+    </row>
+    <row r="668" spans="1:2">
+      <c r="A668" s="5"/>
+      <c r="B668" s="5"/>
+    </row>
+    <row r="669" spans="1:2">
+      <c r="A669" s="5"/>
+      <c r="B669" s="5"/>
+    </row>
+    <row r="670" spans="1:2">
+      <c r="A670" s="5"/>
+      <c r="B670" s="5"/>
+    </row>
+    <row r="671" spans="1:2">
+      <c r="A671" s="5"/>
+      <c r="B671" s="5"/>
+    </row>
+    <row r="672" spans="1:2">
+      <c r="A672" s="5"/>
+      <c r="B672" s="5"/>
+    </row>
+    <row r="673" spans="1:2">
+      <c r="A673" s="5"/>
+      <c r="B673" s="5"/>
+    </row>
+    <row r="674" spans="1:2">
+      <c r="A674" s="5"/>
+      <c r="B674" s="5"/>
+    </row>
+    <row r="675" spans="1:2">
+      <c r="A675" s="5"/>
+      <c r="B675" s="5"/>
+    </row>
+    <row r="676" spans="1:2">
+      <c r="A676" s="5"/>
+      <c r="B676" s="5"/>
+    </row>
+    <row r="677" spans="1:2">
+      <c r="A677" s="5"/>
+      <c r="B677" s="5"/>
+    </row>
+    <row r="678" spans="1:2">
+      <c r="A678" s="5"/>
+      <c r="B678" s="5"/>
+    </row>
+    <row r="679" spans="1:2">
+      <c r="A679" s="5"/>
+      <c r="B679" s="5"/>
+    </row>
+    <row r="680" spans="1:2">
+      <c r="A680" s="5"/>
+      <c r="B680" s="5"/>
+    </row>
+    <row r="681" spans="1:2">
+      <c r="A681" s="5"/>
+      <c r="B681" s="5"/>
+    </row>
+    <row r="682" spans="1:2">
+      <c r="A682" s="5"/>
+      <c r="B682" s="5"/>
+    </row>
+    <row r="683" spans="1:2">
+      <c r="A683" s="5"/>
+      <c r="B683" s="5"/>
+    </row>
+    <row r="684" spans="1:2">
+      <c r="A684" s="5"/>
+      <c r="B684" s="5"/>
+    </row>
+    <row r="685" spans="1:2">
+      <c r="A685" s="5"/>
+      <c r="B685" s="5"/>
+    </row>
+    <row r="686" spans="1:2">
+      <c r="A686" s="5"/>
+      <c r="B686" s="5"/>
+    </row>
+    <row r="687" spans="1:2">
+      <c r="A687" s="5"/>
+      <c r="B687" s="5"/>
+    </row>
+    <row r="688" spans="1:2">
+      <c r="A688" s="5"/>
+      <c r="B688" s="5"/>
+    </row>
+    <row r="689" spans="1:2">
+      <c r="A689" s="5"/>
+      <c r="B689" s="5"/>
+    </row>
+    <row r="690" spans="1:2">
+      <c r="A690" s="5"/>
+      <c r="B690" s="5"/>
+    </row>
+    <row r="691" spans="1:2">
+      <c r="A691" s="5"/>
+      <c r="B691" s="5"/>
+    </row>
+    <row r="692" spans="1:2">
+      <c r="A692" s="5"/>
+      <c r="B692" s="5"/>
+    </row>
+    <row r="693" spans="1:2">
+      <c r="A693" s="5"/>
+      <c r="B693" s="5"/>
+    </row>
+    <row r="694" spans="1:2">
+      <c r="A694" s="5"/>
+      <c r="B694" s="5"/>
+    </row>
+    <row r="695" spans="1:2">
+      <c r="A695" s="5"/>
+      <c r="B695" s="5"/>
+    </row>
+    <row r="696" spans="1:2">
+      <c r="A696" s="5"/>
+      <c r="B696" s="5"/>
+    </row>
+    <row r="697" spans="1:2">
+      <c r="A697" s="5"/>
+      <c r="B697" s="5"/>
+    </row>
+    <row r="698" spans="1:2">
+      <c r="A698" s="5"/>
+      <c r="B698" s="5"/>
+    </row>
+    <row r="699" spans="1:2">
+      <c r="A699" s="5"/>
+      <c r="B699" s="5"/>
+    </row>
+    <row r="700" spans="1:2">
+      <c r="A700" s="5"/>
+      <c r="B700" s="5"/>
+    </row>
+    <row r="701" spans="1:2">
+      <c r="A701" s="5"/>
+      <c r="B701" s="5"/>
+    </row>
+    <row r="702" spans="1:2">
+      <c r="A702" s="5"/>
+      <c r="B702" s="5"/>
+    </row>
+    <row r="703" spans="1:2">
+      <c r="A703" s="5"/>
+      <c r="B703" s="5"/>
+    </row>
+    <row r="704" spans="1:2">
+      <c r="A704" s="5"/>
+      <c r="B704" s="5"/>
+    </row>
+    <row r="705" spans="1:2">
+      <c r="A705" s="5"/>
+      <c r="B705" s="5"/>
+    </row>
+    <row r="706" spans="1:2">
+      <c r="A706" s="5"/>
+      <c r="B706" s="5"/>
+    </row>
+    <row r="707" spans="1:2">
+      <c r="A707" s="5"/>
+      <c r="B707" s="5"/>
+    </row>
+    <row r="708" spans="1:2">
+      <c r="A708" s="5"/>
+      <c r="B708" s="5"/>
+    </row>
+    <row r="709" spans="1:2">
+      <c r="A709" s="5"/>
+      <c r="B709" s="5"/>
+    </row>
+    <row r="710" spans="1:2">
+      <c r="A710" s="5"/>
+      <c r="B710" s="5"/>
+    </row>
+    <row r="711" spans="1:2">
+      <c r="A711" s="5"/>
+      <c r="B711" s="5"/>
+    </row>
+    <row r="712" spans="1:2">
+      <c r="A712" s="5"/>
+      <c r="B712" s="5"/>
+    </row>
+    <row r="713" spans="1:2">
+      <c r="A713" s="5"/>
+      <c r="B713" s="5"/>
+    </row>
+    <row r="714" spans="1:2">
+      <c r="A714" s="5"/>
+      <c r="B714" s="5"/>
+    </row>
+    <row r="715" spans="1:2">
+      <c r="A715" s="5"/>
+      <c r="B715" s="5"/>
+    </row>
+    <row r="716" spans="1:2">
+      <c r="A716" s="5"/>
+      <c r="B716" s="5"/>
+    </row>
+    <row r="717" spans="1:2">
+      <c r="A717" s="5"/>
+      <c r="B717" s="5"/>
+    </row>
+    <row r="718" spans="1:2">
+      <c r="A718" s="5"/>
+      <c r="B718" s="5"/>
+    </row>
+    <row r="719" spans="1:2">
+      <c r="A719" s="5"/>
+      <c r="B719" s="5"/>
+    </row>
+    <row r="720" spans="1:2">
+      <c r="A720" s="5"/>
+      <c r="B720" s="5"/>
+    </row>
+    <row r="721" spans="1:2">
+      <c r="A721" s="5"/>
+      <c r="B721" s="5"/>
+    </row>
+    <row r="722" spans="1:2">
+      <c r="A722" s="5"/>
+      <c r="B722" s="5"/>
+    </row>
+    <row r="723" spans="1:2">
+      <c r="A723" s="5"/>
+      <c r="B723" s="5"/>
+    </row>
+    <row r="724" spans="1:2">
+      <c r="A724" s="5"/>
+      <c r="B724" s="5"/>
+    </row>
+    <row r="725" spans="1:2">
+      <c r="A725" s="5"/>
+      <c r="B725" s="5"/>
+    </row>
+    <row r="726" spans="1:2">
+      <c r="A726" s="5"/>
+      <c r="B726" s="5"/>
+    </row>
+    <row r="727" spans="1:2">
+      <c r="A727" s="5"/>
+      <c r="B727" s="5"/>
+    </row>
+    <row r="728" spans="1:2">
+      <c r="A728" s="5"/>
+      <c r="B728" s="5"/>
+    </row>
+    <row r="729" spans="1:2">
+      <c r="A729" s="5"/>
+      <c r="B729" s="5"/>
+    </row>
+    <row r="730" spans="1:2">
+      <c r="A730" s="5"/>
+      <c r="B730" s="5"/>
+    </row>
+    <row r="731" spans="1:2">
+      <c r="A731" s="5"/>
+      <c r="B731" s="5"/>
+    </row>
+    <row r="732" spans="1:2">
+      <c r="A732" s="5"/>
+      <c r="B732" s="5"/>
+    </row>
+    <row r="733" spans="1:2">
+      <c r="A733" s="5"/>
+      <c r="B733" s="5"/>
+    </row>
+    <row r="734" spans="1:2">
+      <c r="A734" s="5"/>
+      <c r="B734" s="5"/>
+    </row>
+    <row r="735" spans="1:2">
+      <c r="A735" s="5"/>
+      <c r="B735" s="5"/>
+    </row>
+    <row r="736" spans="1:2">
+      <c r="A736" s="5"/>
+      <c r="B736" s="5"/>
+    </row>
+    <row r="737" spans="1:2">
+      <c r="A737" s="5"/>
+      <c r="B737" s="5"/>
+    </row>
+    <row r="738" spans="1:2">
+      <c r="A738" s="5"/>
+      <c r="B738" s="5"/>
+    </row>
+    <row r="739" spans="1:2">
+      <c r="A739" s="5"/>
+      <c r="B739" s="5"/>
+    </row>
+    <row r="740" spans="1:2">
+      <c r="A740" s="5"/>
+      <c r="B740" s="5"/>
+    </row>
+    <row r="741" spans="1:2">
+      <c r="A741" s="5"/>
+      <c r="B741" s="5"/>
+    </row>
+    <row r="742" spans="1:2">
+      <c r="A742" s="5"/>
+      <c r="B742" s="5"/>
+    </row>
+    <row r="743" spans="1:2">
+      <c r="A743" s="5"/>
+      <c r="B743" s="5"/>
+    </row>
+    <row r="744" spans="1:2">
+      <c r="A744" s="5"/>
+      <c r="B744" s="5"/>
+    </row>
+    <row r="745" spans="1:2">
+      <c r="A745" s="5"/>
+      <c r="B745" s="5"/>
+    </row>
+    <row r="746" spans="1:2">
+      <c r="A746" s="5"/>
+      <c r="B746" s="5"/>
+    </row>
+    <row r="747" spans="1:2">
+      <c r="A747" s="5"/>
+      <c r="B747" s="5"/>
+    </row>
+    <row r="748" spans="1:2">
+      <c r="A748" s="5"/>
+      <c r="B748" s="5"/>
+    </row>
+    <row r="749" spans="1:2">
+      <c r="A749" s="5"/>
+      <c r="B749" s="5"/>
+    </row>
+    <row r="750" spans="1:2">
+      <c r="A750" s="5"/>
+      <c r="B750" s="5"/>
+    </row>
+    <row r="751" spans="1:2">
+      <c r="A751" s="5"/>
+      <c r="B751" s="5"/>
+    </row>
+    <row r="752" spans="1:2">
+      <c r="A752" s="5"/>
+      <c r="B752" s="5"/>
+    </row>
+    <row r="753" spans="1:2">
+      <c r="A753" s="5"/>
+      <c r="B753" s="5"/>
+    </row>
+    <row r="754" spans="1:2">
+      <c r="A754" s="5"/>
+      <c r="B754" s="5"/>
+    </row>
+    <row r="755" spans="1:2">
+      <c r="A755" s="5"/>
+      <c r="B755" s="5"/>
+    </row>
+    <row r="756" spans="1:2">
+      <c r="A756" s="5"/>
+      <c r="B756" s="5"/>
+    </row>
+    <row r="757" spans="1:2">
+      <c r="A757" s="5"/>
+      <c r="B757" s="5"/>
+    </row>
+    <row r="758" spans="1:2">
+      <c r="A758" s="5"/>
+      <c r="B758" s="5"/>
+    </row>
+    <row r="759" spans="1:2">
+      <c r="A759" s="5"/>
+      <c r="B759" s="5"/>
+    </row>
+    <row r="760" spans="1:2">
+      <c r="A760" s="5"/>
+      <c r="B760" s="5"/>
+    </row>
+    <row r="761" spans="1:2">
+      <c r="A761" s="5"/>
+      <c r="B761" s="5"/>
+    </row>
+    <row r="762" spans="1:2">
+      <c r="A762" s="5"/>
+      <c r="B762" s="5"/>
+    </row>
+    <row r="763" spans="1:2">
+      <c r="A763" s="5"/>
+      <c r="B763" s="5"/>
+    </row>
+    <row r="764" spans="1:2">
+      <c r="A764" s="5"/>
+      <c r="B764" s="5"/>
+    </row>
+    <row r="765" spans="1:2">
+      <c r="A765" s="5"/>
+      <c r="B765" s="5"/>
+    </row>
+    <row r="766" spans="1:2">
+      <c r="A766" s="5"/>
+      <c r="B766" s="5"/>
+    </row>
+    <row r="767" spans="1:2">
+      <c r="A767" s="5"/>
+      <c r="B767" s="5"/>
+    </row>
+    <row r="768" spans="1:2">
+      <c r="A768" s="5"/>
+      <c r="B768" s="5"/>
+    </row>
+    <row r="769" spans="1:2">
+      <c r="A769" s="5"/>
+      <c r="B769" s="5"/>
+    </row>
+    <row r="770" spans="1:2">
+      <c r="A770" s="5"/>
+      <c r="B770" s="5"/>
+    </row>
+    <row r="771" spans="1:2">
+      <c r="A771" s="5"/>
+      <c r="B771" s="5"/>
+    </row>
+    <row r="772" spans="1:2">
+      <c r="A772" s="5"/>
+      <c r="B772" s="5"/>
+    </row>
+    <row r="773" spans="1:2">
+      <c r="A773" s="5"/>
+      <c r="B773" s="5"/>
+    </row>
+    <row r="774" spans="1:2">
+      <c r="A774" s="5"/>
+      <c r="B774" s="5"/>
+    </row>
+    <row r="775" spans="1:2">
+      <c r="A775" s="5"/>
+      <c r="B775" s="5"/>
+    </row>
+    <row r="776" spans="1:2">
+      <c r="A776" s="5"/>
+      <c r="B776" s="5"/>
+    </row>
+    <row r="777" spans="1:2">
+      <c r="A777" s="5"/>
+      <c r="B777" s="5"/>
+    </row>
+    <row r="778" spans="1:2">
+      <c r="A778" s="5"/>
+      <c r="B778" s="5"/>
+    </row>
+    <row r="779" spans="1:2">
+      <c r="A779" s="5"/>
+      <c r="B779" s="5"/>
+    </row>
+    <row r="780" spans="1:2">
+      <c r="A780" s="5"/>
+      <c r="B780" s="5"/>
+    </row>
+    <row r="781" spans="1:2">
+      <c r="A781" s="5"/>
+      <c r="B781" s="5"/>
+    </row>
+    <row r="782" spans="1:2">
+      <c r="A782" s="5"/>
+      <c r="B782" s="5"/>
+    </row>
+    <row r="783" spans="1:2">
+      <c r="A783" s="5"/>
+      <c r="B783" s="5"/>
+    </row>
+    <row r="784" spans="1:2">
+      <c r="A784" s="5"/>
+      <c r="B784" s="5"/>
+    </row>
+    <row r="785" spans="1:2">
+      <c r="A785" s="5"/>
+      <c r="B785" s="5"/>
+    </row>
+    <row r="786" spans="1:2">
+      <c r="A786" s="5"/>
+      <c r="B786" s="5"/>
+    </row>
+    <row r="787" spans="1:2">
+      <c r="A787" s="5"/>
+      <c r="B787" s="5"/>
+    </row>
+    <row r="788" spans="1:2">
+      <c r="A788" s="5"/>
+      <c r="B788" s="5"/>
+    </row>
+    <row r="789" spans="1:2">
+      <c r="A789" s="5"/>
+      <c r="B789" s="5"/>
+    </row>
+    <row r="790" spans="1:2">
+      <c r="A790" s="5"/>
+      <c r="B790" s="5"/>
+    </row>
+    <row r="791" spans="1:2">
+      <c r="A791" s="5"/>
+      <c r="B791" s="5"/>
+    </row>
+    <row r="792" spans="1:2">
+      <c r="A792" s="5"/>
+      <c r="B792" s="5"/>
+    </row>
+    <row r="793" spans="1:2">
+      <c r="A793" s="5"/>
+      <c r="B793" s="5"/>
+    </row>
+    <row r="794" spans="1:2">
+      <c r="A794" s="5"/>
+      <c r="B794" s="5"/>
+    </row>
+    <row r="795" spans="1:2">
+      <c r="A795" s="5"/>
+      <c r="B795" s="5"/>
+    </row>
+    <row r="796" spans="1:2">
+      <c r="A796" s="5"/>
+      <c r="B796" s="5"/>
+    </row>
+    <row r="797" spans="1:2">
+      <c r="A797" s="5"/>
+      <c r="B797" s="5"/>
+    </row>
+    <row r="798" spans="1:2">
+      <c r="A798" s="5"/>
+      <c r="B798" s="5"/>
+    </row>
+    <row r="799" spans="1:2">
+      <c r="A799" s="5"/>
+      <c r="B799" s="5"/>
+    </row>
+    <row r="800" spans="1:2">
+      <c r="A800" s="5"/>
+      <c r="B800" s="5"/>
+    </row>
+    <row r="801" spans="1:2">
+      <c r="A801" s="5"/>
+      <c r="B801" s="5"/>
+    </row>
+    <row r="802" spans="1:2">
+      <c r="A802" s="5"/>
+      <c r="B802" s="5"/>
+    </row>
+    <row r="803" spans="1:2">
+      <c r="A803" s="5"/>
+      <c r="B803" s="5"/>
+    </row>
+    <row r="804" spans="1:2">
+      <c r="A804" s="5"/>
+      <c r="B804" s="5"/>
+    </row>
+    <row r="805" spans="1:2">
+      <c r="A805" s="5"/>
+      <c r="B805" s="5"/>
+    </row>
+    <row r="806" spans="1:2">
+      <c r="A806" s="5"/>
+      <c r="B806" s="5"/>
+    </row>
+    <row r="807" spans="1:2">
+      <c r="A807" s="5"/>
+      <c r="B807" s="5"/>
+    </row>
+    <row r="808" spans="1:2">
+      <c r="A808" s="5"/>
+      <c r="B808" s="5"/>
+    </row>
+    <row r="809" spans="1:2">
+      <c r="A809" s="5"/>
+      <c r="B809" s="5"/>
+    </row>
+    <row r="810" spans="1:2">
+      <c r="A810" s="5"/>
+      <c r="B810" s="5"/>
+    </row>
+    <row r="811" spans="1:2">
+      <c r="A811" s="5"/>
+      <c r="B811" s="5"/>
+    </row>
+    <row r="812" spans="1:2">
+      <c r="A812" s="5"/>
+      <c r="B812" s="5"/>
+    </row>
+    <row r="813" spans="1:2">
+      <c r="A813" s="5"/>
+      <c r="B813" s="5"/>
+    </row>
+    <row r="814" spans="1:2">
+      <c r="A814" s="5"/>
+      <c r="B814" s="5"/>
+    </row>
+    <row r="815" spans="1:2">
+      <c r="A815" s="5"/>
+      <c r="B815" s="5"/>
+    </row>
+    <row r="816" spans="1:2">
+      <c r="A816" s="5"/>
+      <c r="B816" s="5"/>
+    </row>
+    <row r="817" spans="1:2">
+      <c r="A817" s="5"/>
+      <c r="B817" s="5"/>
+    </row>
+    <row r="818" spans="1:2">
+      <c r="A818" s="5"/>
+      <c r="B818" s="5"/>
+    </row>
+    <row r="819" spans="1:2">
+      <c r="A819" s="5"/>
+      <c r="B819" s="5"/>
+    </row>
+    <row r="820" spans="1:2">
+      <c r="A820" s="5"/>
+      <c r="B820" s="5"/>
+    </row>
+    <row r="821" spans="1:2">
+      <c r="A821" s="5"/>
+      <c r="B821" s="5"/>
+    </row>
+    <row r="822" spans="1:2">
+      <c r="A822" s="5"/>
+      <c r="B822" s="5"/>
+    </row>
+    <row r="823" spans="1:2">
+      <c r="A823" s="5"/>
+      <c r="B823" s="5"/>
+    </row>
+    <row r="824" spans="1:2">
+      <c r="A824" s="5"/>
+      <c r="B824" s="5"/>
+    </row>
+    <row r="825" spans="1:2">
+      <c r="A825" s="5"/>
+      <c r="B825" s="5"/>
+    </row>
+    <row r="826" spans="1:2">
+      <c r="A826" s="5"/>
+      <c r="B826" s="5"/>
+    </row>
+    <row r="827" spans="1:2">
+      <c r="A827" s="5"/>
+      <c r="B827" s="5"/>
+    </row>
+    <row r="828" spans="1:2">
+      <c r="A828" s="5"/>
+      <c r="B828" s="5"/>
+    </row>
+    <row r="829" spans="1:2">
+      <c r="A829" s="5"/>
+      <c r="B829" s="5"/>
+    </row>
+    <row r="830" spans="1:2">
+      <c r="A830" s="5"/>
+      <c r="B830" s="5"/>
+    </row>
+    <row r="831" spans="1:2">
+      <c r="A831" s="5"/>
+      <c r="B831" s="5"/>
+    </row>
+    <row r="832" spans="1:2">
+      <c r="A832" s="5"/>
+      <c r="B832" s="5"/>
+    </row>
+    <row r="833" spans="1:2">
+      <c r="A833" s="5"/>
+      <c r="B833" s="5"/>
+    </row>
+    <row r="834" spans="1:2">
+      <c r="A834" s="5"/>
+      <c r="B834" s="5"/>
+    </row>
+    <row r="835" spans="1:2">
+      <c r="A835" s="5"/>
+      <c r="B835" s="5"/>
+    </row>
+    <row r="836" spans="1:2">
+      <c r="A836" s="5"/>
+      <c r="B836" s="5"/>
+    </row>
+    <row r="837" spans="1:2">
+      <c r="A837" s="5"/>
+      <c r="B837" s="5"/>
+    </row>
+    <row r="838" spans="1:2">
+      <c r="A838" s="5"/>
+      <c r="B838" s="5"/>
+    </row>
+    <row r="839" spans="1:2">
+      <c r="A839" s="5"/>
+      <c r="B839" s="5"/>
+    </row>
+    <row r="840" spans="1:2">
+      <c r="A840" s="5"/>
+      <c r="B840" s="5"/>
+    </row>
+    <row r="841" spans="1:2">
+      <c r="A841" s="5"/>
+      <c r="B841" s="5"/>
+    </row>
+    <row r="842" spans="1:2">
+      <c r="A842" s="5"/>
+      <c r="B842" s="5"/>
+    </row>
+    <row r="843" spans="1:2">
+      <c r="A843" s="5"/>
+      <c r="B843" s="5"/>
+    </row>
+    <row r="844" spans="1:2">
+      <c r="A844" s="5"/>
+      <c r="B844" s="5"/>
+    </row>
+    <row r="845" spans="1:2">
+      <c r="A845" s="5"/>
+      <c r="B845" s="5"/>
+    </row>
+    <row r="846" spans="1:2">
+      <c r="A846" s="5"/>
+      <c r="B846" s="5"/>
+    </row>
+    <row r="847" spans="1:2">
+      <c r="A847" s="5"/>
+      <c r="B847" s="5"/>
+    </row>
+    <row r="848" spans="1:2">
+      <c r="A848" s="5"/>
+      <c r="B848" s="5"/>
+    </row>
+    <row r="849" spans="1:2">
+      <c r="A849" s="5"/>
+      <c r="B849" s="5"/>
+    </row>
+    <row r="850" spans="1:2">
+      <c r="A850" s="5"/>
+      <c r="B850" s="5"/>
+    </row>
+    <row r="851" spans="1:2">
+      <c r="A851" s="5"/>
+      <c r="B851" s="5"/>
+    </row>
+    <row r="852" spans="1:2">
+      <c r="A852" s="5"/>
+      <c r="B852" s="5"/>
+    </row>
+    <row r="853" spans="1:2">
+      <c r="A853" s="5"/>
+      <c r="B853" s="5"/>
+    </row>
+    <row r="854" spans="1:2">
+      <c r="A854" s="5"/>
+      <c r="B854" s="5"/>
+    </row>
+    <row r="855" spans="1:2">
+      <c r="A855" s="5"/>
+      <c r="B855" s="5"/>
+    </row>
+    <row r="856" spans="1:2">
+      <c r="A856" s="5"/>
+      <c r="B856" s="5"/>
+    </row>
+    <row r="857" spans="1:2">
+      <c r="A857" s="5"/>
+      <c r="B857" s="5"/>
+    </row>
+    <row r="858" spans="1:2">
+      <c r="A858" s="5"/>
+      <c r="B858" s="5"/>
+    </row>
+    <row r="859" spans="1:2">
+      <c r="A859" s="5"/>
+      <c r="B859" s="5"/>
+    </row>
+    <row r="860" spans="1:2">
+      <c r="A860" s="5"/>
+      <c r="B860" s="5"/>
+    </row>
+    <row r="861" spans="1:2">
+      <c r="A861" s="5"/>
+      <c r="B861" s="5"/>
+    </row>
+    <row r="862" spans="1:2">
+      <c r="A862" s="5"/>
+      <c r="B862" s="5"/>
+    </row>
+    <row r="863" spans="1:2">
+      <c r="A863" s="5"/>
+      <c r="B863" s="5"/>
+    </row>
+    <row r="864" spans="1:2">
+      <c r="A864" s="5"/>
+      <c r="B864" s="5"/>
+    </row>
+    <row r="865" spans="1:2">
+      <c r="A865" s="5"/>
+      <c r="B865" s="5"/>
+    </row>
+    <row r="866" spans="1:2">
+      <c r="A866" s="5"/>
+      <c r="B866" s="5"/>
+    </row>
+    <row r="867" spans="1:2">
+      <c r="A867" s="5"/>
+      <c r="B867" s="5"/>
+    </row>
+    <row r="868" spans="1:2">
+      <c r="A868" s="5"/>
+      <c r="B868" s="5"/>
+    </row>
+    <row r="869" spans="1:2">
+      <c r="A869" s="5"/>
+      <c r="B869" s="5"/>
+    </row>
+    <row r="870" spans="1:2">
+      <c r="A870" s="5"/>
+      <c r="B870" s="5"/>
+    </row>
+    <row r="871" spans="1:2">
+      <c r="A871" s="5"/>
+      <c r="B871" s="5"/>
+    </row>
+    <row r="872" spans="1:2">
+      <c r="A872" s="5"/>
+      <c r="B872" s="5"/>
+    </row>
+    <row r="873" spans="1:2">
+      <c r="A873" s="5"/>
+      <c r="B873" s="5"/>
+    </row>
+    <row r="874" spans="1:2">
+      <c r="A874" s="5"/>
+      <c r="B874" s="5"/>
+    </row>
+    <row r="875" spans="1:2">
+      <c r="A875" s="5"/>
+      <c r="B875" s="5"/>
+    </row>
+    <row r="876" spans="1:2">
+      <c r="A876" s="5"/>
+      <c r="B876" s="5"/>
+    </row>
+    <row r="877" spans="1:2">
+      <c r="A877" s="5"/>
+      <c r="B877" s="5"/>
+    </row>
+    <row r="878" spans="1:2">
+      <c r="A878" s="5"/>
+      <c r="B878" s="5"/>
+    </row>
+    <row r="879" spans="1:2">
+      <c r="A879" s="5"/>
+      <c r="B879" s="5"/>
+    </row>
+    <row r="880" spans="1:2">
+      <c r="A880" s="5"/>
+      <c r="B880" s="5"/>
+    </row>
+    <row r="881" spans="1:2">
+      <c r="A881" s="5"/>
+      <c r="B881" s="5"/>
+    </row>
+    <row r="882" spans="1:2">
+      <c r="A882" s="5"/>
+      <c r="B882" s="5"/>
+    </row>
+    <row r="883" spans="1:2">
+      <c r="A883" s="5"/>
+      <c r="B883" s="5"/>
+    </row>
+    <row r="884" spans="1:2">
+      <c r="A884" s="5"/>
+      <c r="B884" s="5"/>
+    </row>
+    <row r="885" spans="1:2">
+      <c r="A885" s="5"/>
+      <c r="B885" s="5"/>
+    </row>
+    <row r="886" spans="1:2">
+      <c r="A886" s="5"/>
+      <c r="B886" s="5"/>
+    </row>
+    <row r="887" spans="1:2">
+      <c r="A887" s="5"/>
+      <c r="B887" s="5"/>
+    </row>
+    <row r="888" spans="1:2">
+      <c r="A888" s="5"/>
+      <c r="B888" s="5"/>
+    </row>
+    <row r="889" spans="1:2">
+      <c r="A889" s="5"/>
+      <c r="B889" s="5"/>
+    </row>
+    <row r="890" spans="1:2">
+      <c r="A890" s="5"/>
+      <c r="B890" s="5"/>
+    </row>
+    <row r="891" spans="1:2">
+      <c r="A891" s="5"/>
+      <c r="B891" s="5"/>
+    </row>
+    <row r="892" spans="1:2">
+      <c r="A892" s="5"/>
+      <c r="B892" s="5"/>
+    </row>
+    <row r="893" spans="1:2">
+      <c r="A893" s="5"/>
+      <c r="B893" s="5"/>
+    </row>
+    <row r="894" spans="1:2">
+      <c r="A894" s="5"/>
+      <c r="B894" s="5"/>
+    </row>
+    <row r="895" spans="1:2">
+      <c r="A895" s="5"/>
+      <c r="B895" s="5"/>
+    </row>
+    <row r="896" spans="1:2">
+      <c r="A896" s="5"/>
+      <c r="B896" s="5"/>
+    </row>
+    <row r="897" spans="1:2">
+      <c r="A897" s="5"/>
+      <c r="B897" s="5"/>
+    </row>
+    <row r="898" spans="1:2">
+      <c r="A898" s="5"/>
+      <c r="B898" s="5"/>
+    </row>
+    <row r="899" spans="1:2">
+      <c r="A899" s="5"/>
+      <c r="B899" s="5"/>
+    </row>
+    <row r="900" spans="1:2">
+      <c r="A900" s="5"/>
+      <c r="B900" s="5"/>
+    </row>
+    <row r="901" spans="1:2">
+      <c r="A901" s="5"/>
+      <c r="B901" s="5"/>
+    </row>
+    <row r="902" spans="1:2">
+      <c r="A902" s="5"/>
+      <c r="B902" s="5"/>
+    </row>
+    <row r="903" spans="1:2">
+      <c r="A903" s="5"/>
+      <c r="B903" s="5"/>
+    </row>
+    <row r="904" spans="1:2">
+      <c r="A904" s="5"/>
+      <c r="B904" s="5"/>
+    </row>
+    <row r="905" spans="1:2">
+      <c r="A905" s="5"/>
+      <c r="B905" s="5"/>
+    </row>
+    <row r="906" spans="1:2">
+      <c r="A906" s="5"/>
+      <c r="B906" s="5"/>
+    </row>
+    <row r="907" spans="1:2">
+      <c r="A907" s="5"/>
+      <c r="B907" s="5"/>
+    </row>
+    <row r="908" spans="1:2">
+      <c r="A908" s="5"/>
+      <c r="B908" s="5"/>
+    </row>
+    <row r="909" spans="1:2">
+      <c r="A909" s="5"/>
+      <c r="B909" s="5"/>
+    </row>
+    <row r="910" spans="1:2">
+      <c r="A910" s="5"/>
+      <c r="B910" s="5"/>
+    </row>
+    <row r="911" spans="1:2">
+      <c r="A911" s="5"/>
+      <c r="B911" s="5"/>
+    </row>
+    <row r="912" spans="1:2">
+      <c r="A912" s="5"/>
+      <c r="B912" s="5"/>
+    </row>
+    <row r="913" spans="1:2">
+      <c r="A913" s="5"/>
+      <c r="B913" s="5"/>
+    </row>
+    <row r="914" spans="1:2">
+      <c r="A914" s="5"/>
+      <c r="B914" s="5"/>
+    </row>
+    <row r="915" spans="1:2">
+      <c r="A915" s="5"/>
+      <c r="B915" s="5"/>
+    </row>
+    <row r="916" spans="1:2">
+      <c r="A916" s="5"/>
+      <c r="B916" s="5"/>
+    </row>
+    <row r="917" spans="1:2">
+      <c r="A917" s="5"/>
+      <c r="B917" s="5"/>
+    </row>
+    <row r="918" spans="1:2">
+      <c r="A918" s="5"/>
+      <c r="B918" s="5"/>
+    </row>
+    <row r="919" spans="1:2">
+      <c r="A919" s="5"/>
+      <c r="B919" s="5"/>
+    </row>
+    <row r="920" spans="1:2">
+      <c r="A920" s="5"/>
+      <c r="B920" s="5"/>
+    </row>
+    <row r="921" spans="1:2">
+      <c r="A921" s="5"/>
+      <c r="B921" s="5"/>
+    </row>
+    <row r="922" spans="1:2">
+      <c r="A922" s="5"/>
+      <c r="B922" s="5"/>
+    </row>
+    <row r="923" spans="1:2">
+      <c r="A923" s="5"/>
+      <c r="B923" s="5"/>
+    </row>
+    <row r="924" spans="1:2">
+      <c r="A924" s="5"/>
+      <c r="B924" s="5"/>
+    </row>
+    <row r="925" spans="1:2">
+      <c r="A925" s="5"/>
+      <c r="B925" s="5"/>
+    </row>
+    <row r="926" spans="1:2">
+      <c r="A926" s="5"/>
+      <c r="B926" s="5"/>
+    </row>
+    <row r="927" spans="1:2">
+      <c r="A927" s="5"/>
+      <c r="B927" s="5"/>
+    </row>
+    <row r="928" spans="1:2">
+      <c r="A928" s="5"/>
+      <c r="B928" s="5"/>
+    </row>
+    <row r="929" spans="1:2">
+      <c r="A929" s="5"/>
+      <c r="B929" s="5"/>
+    </row>
+    <row r="930" spans="1:2">
+      <c r="A930" s="5"/>
+      <c r="B930" s="5"/>
+    </row>
+    <row r="931" spans="1:2">
+      <c r="A931" s="5"/>
+      <c r="B931" s="5"/>
+    </row>
+    <row r="932" spans="1:2">
+      <c r="A932" s="5"/>
+      <c r="B932" s="5"/>
+    </row>
+    <row r="933" spans="1:2">
+      <c r="A933" s="5"/>
+      <c r="B933" s="5"/>
+    </row>
+    <row r="934" spans="1:2">
+      <c r="A934" s="5"/>
+      <c r="B934" s="5"/>
+    </row>
+    <row r="935" spans="1:2">
+      <c r="A935" s="5"/>
+      <c r="B935" s="5"/>
+    </row>
+    <row r="936" spans="1:2">
+      <c r="A936" s="5"/>
+      <c r="B936" s="5"/>
+    </row>
+    <row r="937" spans="1:2">
+      <c r="A937" s="5"/>
+      <c r="B937" s="5"/>
+    </row>
+    <row r="938" spans="1:2">
+      <c r="A938" s="5"/>
+      <c r="B938" s="5"/>
+    </row>
+    <row r="939" spans="1:2">
+      <c r="A939" s="5"/>
+      <c r="B939" s="5"/>
+    </row>
+    <row r="940" spans="1:2">
+      <c r="A940" s="5"/>
+      <c r="B940" s="5"/>
+    </row>
+    <row r="941" spans="1:2">
+      <c r="A941" s="5"/>
+      <c r="B941" s="5"/>
+    </row>
+    <row r="942" spans="1:2">
+      <c r="A942" s="5"/>
+      <c r="B942" s="5"/>
+    </row>
+    <row r="943" spans="1:2">
+      <c r="A943" s="5"/>
+      <c r="B943" s="5"/>
+    </row>
+    <row r="944" spans="1:2">
+      <c r="A944" s="5"/>
+      <c r="B944" s="5"/>
+    </row>
+    <row r="945" spans="1:2">
+      <c r="A945" s="5"/>
+      <c r="B945" s="5"/>
+    </row>
+    <row r="946" spans="1:2">
+      <c r="A946" s="5"/>
+      <c r="B946" s="5"/>
+    </row>
+    <row r="947" spans="1:2">
+      <c r="A947" s="5"/>
+      <c r="B947" s="5"/>
+    </row>
+    <row r="948" spans="1:2">
+      <c r="A948" s="5"/>
+      <c r="B948" s="5"/>
+    </row>
+    <row r="949" spans="1:2">
+      <c r="A949" s="5"/>
+      <c r="B949" s="5"/>
+    </row>
+    <row r="950" spans="1:2">
+      <c r="A950" s="5"/>
+      <c r="B950" s="5"/>
+    </row>
+    <row r="951" spans="1:2">
+      <c r="A951" s="5"/>
+      <c r="B951" s="5"/>
+    </row>
+    <row r="952" spans="1:2">
+      <c r="A952" s="5"/>
+      <c r="B952" s="5"/>
+    </row>
+    <row r="953" spans="1:2">
+      <c r="A953" s="5"/>
+      <c r="B953" s="5"/>
+    </row>
+    <row r="954" spans="1:2">
+      <c r="A954" s="5"/>
+      <c r="B954" s="5"/>
+    </row>
+    <row r="955" spans="1:2">
+      <c r="A955" s="5"/>
+      <c r="B955" s="5"/>
+    </row>
+    <row r="956" spans="1:2">
+      <c r="A956" s="5"/>
+      <c r="B956" s="5"/>
+    </row>
+    <row r="957" spans="1:2">
+      <c r="A957" s="5"/>
+      <c r="B957" s="5"/>
+    </row>
+    <row r="958" spans="1:2">
+      <c r="A958" s="5"/>
+      <c r="B958" s="5"/>
+    </row>
+    <row r="959" spans="1:2">
+      <c r="A959" s="5"/>
+      <c r="B959" s="5"/>
+    </row>
+    <row r="960" spans="1:2">
+      <c r="A960" s="5"/>
+      <c r="B960" s="5"/>
+    </row>
+    <row r="961" spans="1:2">
+      <c r="A961" s="5"/>
+      <c r="B961" s="5"/>
+    </row>
+    <row r="962" spans="1:2">
+      <c r="A962" s="5"/>
+      <c r="B962" s="5"/>
+    </row>
+    <row r="963" spans="1:2">
+      <c r="A963" s="5"/>
+      <c r="B963" s="5"/>
+    </row>
+    <row r="964" spans="1:2">
+      <c r="A964" s="5"/>
+      <c r="B964" s="5"/>
+    </row>
+    <row r="965" spans="1:2">
+      <c r="A965" s="5"/>
+      <c r="B965" s="5"/>
+    </row>
+    <row r="966" spans="1:2">
+      <c r="A966" s="5"/>
+      <c r="B966" s="5"/>
+    </row>
+    <row r="967" spans="1:2">
+      <c r="A967" s="5"/>
+      <c r="B967" s="5"/>
+    </row>
+    <row r="968" spans="1:2">
+      <c r="A968" s="5"/>
+      <c r="B968" s="5"/>
+    </row>
+    <row r="969" spans="1:2">
+      <c r="A969" s="5"/>
+      <c r="B969" s="5"/>
+    </row>
+    <row r="970" spans="1:2">
+      <c r="A970" s="5"/>
+      <c r="B970" s="5"/>
+    </row>
+    <row r="971" spans="1:2">
+      <c r="A971" s="5"/>
+      <c r="B971" s="5"/>
+    </row>
+    <row r="972" spans="1:2">
+      <c r="A972" s="5"/>
+      <c r="B972" s="5"/>
+    </row>
+    <row r="973" spans="1:2">
+      <c r="A973" s="5"/>
+      <c r="B973" s="5"/>
+    </row>
+    <row r="974" spans="1:2">
+      <c r="A974" s="5"/>
+      <c r="B974" s="5"/>
+    </row>
+    <row r="975" spans="1:2">
+      <c r="A975" s="5"/>
+      <c r="B975" s="5"/>
+    </row>
+    <row r="976" spans="1:2">
+      <c r="A976" s="5"/>
+      <c r="B976" s="5"/>
+    </row>
+    <row r="977" spans="1:2">
+      <c r="A977" s="5"/>
+      <c r="B977" s="5"/>
+    </row>
+    <row r="978" spans="1:2">
+      <c r="A978" s="5"/>
+      <c r="B978" s="5"/>
+    </row>
+    <row r="979" spans="1:2">
+      <c r="A979" s="5"/>
+      <c r="B979" s="5"/>
+    </row>
+    <row r="980" spans="1:2">
+      <c r="A980" s="5"/>
+      <c r="B980" s="5"/>
+    </row>
+    <row r="981" spans="1:2">
+      <c r="A981" s="5"/>
+      <c r="B981" s="5"/>
+    </row>
+    <row r="982" spans="1:2">
+      <c r="A982" s="5"/>
+      <c r="B982" s="5"/>
+    </row>
+    <row r="983" spans="1:2">
+      <c r="A983" s="5"/>
+      <c r="B983" s="5"/>
+    </row>
+    <row r="984" spans="1:2">
+      <c r="A984" s="5"/>
+      <c r="B984" s="5"/>
+    </row>
+    <row r="985" spans="1:2">
+      <c r="A985" s="5"/>
+      <c r="B985" s="5"/>
+    </row>
+    <row r="986" spans="1:2">
+      <c r="A986" s="5"/>
+      <c r="B986" s="5"/>
+    </row>
+    <row r="987" spans="1:2">
+      <c r="A987" s="5"/>
+      <c r="B987" s="5"/>
+    </row>
+    <row r="988" spans="1:2">
+      <c r="A988" s="5"/>
+      <c r="B988" s="5"/>
+    </row>
+    <row r="989" spans="1:2">
+      <c r="A989" s="5"/>
+      <c r="B989" s="5"/>
+    </row>
+    <row r="990" spans="1:2">
+      <c r="A990" s="5"/>
+      <c r="B990" s="5"/>
+    </row>
+    <row r="991" spans="1:2">
+      <c r="A991" s="5"/>
+      <c r="B991" s="5"/>
+    </row>
+    <row r="992" spans="1:2">
+      <c r="A992" s="5"/>
+      <c r="B992" s="5"/>
+    </row>
+    <row r="993" spans="1:2">
+      <c r="A993" s="5"/>
+      <c r="B993" s="5"/>
+    </row>
+    <row r="994" spans="1:2">
+      <c r="A994" s="5"/>
+      <c r="B994" s="5"/>
+    </row>
+    <row r="995" spans="1:2">
+      <c r="A995" s="5"/>
+      <c r="B995" s="5"/>
+    </row>
+    <row r="996" spans="1:2">
+      <c r="A996" s="5"/>
+      <c r="B996" s="5"/>
+    </row>
+    <row r="997" spans="1:2">
+      <c r="A997" s="5"/>
+      <c r="B997" s="5"/>
+    </row>
+    <row r="998" spans="1:2">
+      <c r="A998" s="5"/>
+      <c r="B998" s="5"/>
+    </row>
+    <row r="999" spans="1:2">
+      <c r="A999" s="5"/>
+      <c r="B999" s="5"/>
+    </row>
+    <row r="1000" spans="1:2">
+      <c r="A1000" s="5"/>
+      <c r="B1000" s="5"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C181" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>"Enjoyment,Sadness,Anger,Fear,Disgust,Surprise,Other"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>